--- a/data/ensemble-scores.xlsx
+++ b/data/ensemble-scores.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Scores" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Scores!$A$1:$AI$932</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Scores!$A$1:$AI$935</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10288" uniqueCount="5799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10331" uniqueCount="5829">
   <si>
     <t>編成人数</t>
   </si>
@@ -18309,6 +18309,101 @@
   <si>
     <t>https://www.trevcomusic.com/cdn/shop/products/BOC29Page5_1024x1024.jpeg?v=1571437754</t>
   </si>
+  <si>
+    <t>Fg×6</t>
+  </si>
+  <si>
+    <t>Konzertstück</t>
+  </si>
+  <si>
+    <t>ACC4020</t>
+  </si>
+  <si>
+    <t>M501351169</t>
+  </si>
+  <si>
+    <t>https://www.academia-music.com/upload/save_image/1501752978.jpg</t>
+  </si>
+  <si>
+    <t>https://www.academia-music.com/upload/save_image/1501752978_2.jpg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/928DiFo2AF8?si=G8IEa6yM1OvepKIr</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V2205b4XQaM?si=fRvyvXeGv8lVgpjM&amp;t=30</t>
+  </si>
+  <si>
+    <t>Fg×2 + Pf</t>
+  </si>
+  <si>
+    <t>Concertino</t>
+  </si>
+  <si>
+    <t>ACC1030k</t>
+  </si>
+  <si>
+    <t>2本のバスーンとオーケストラ(またはピアノ)を組み合わせた演奏会のプログラムなら、ぜひ毎回取り上げたい一曲。第2楽章は雄弁で、胸が締めつけられるほど美しく、両端の楽章はソリスト同士のバランスも含めて、楽しく見事に書かれています。これは間違いなく傑作! メロディアスで親しみやすく、誰の耳にもすっと入ってくる音楽です。印象に残る、そして「もう一度聴きたい」と思わせる新作です!</t>
+  </si>
+  <si>
+    <t>I. Poco lento- Allegro bucolico
+II. Andante flessibile
+III. Allegro spiritoso</t>
+  </si>
+  <si>
+    <t>https://www.trevcomusic.com/cdn/shop/products/ACC1030kCover_1024x1024.jpeg?v=1571437377</t>
+  </si>
+  <si>
+    <t>https://www.trevcomusic.com/cdn/shop/products/ACC1030kPage1_1024x1024.jpeg?v=1571437377</t>
+  </si>
+  <si>
+    <t>https://www.trevcomusic.com/cdn/shop/products/ACC1030kPage2_1024x1024.jpeg?v=1571437377</t>
+  </si>
+  <si>
+    <t>https://youtu.be/PM18KTuYNtA?si=z7cfKpQT8TEWShqM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DH5iV4FMeKY?si=fDKB52gV2c_MSAIo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Y7fFb-F9ZyE?si=MI1QdPKX0F6ho-8E</t>
+  </si>
+  <si>
+    <t>Fg×3</t>
+  </si>
+  <si>
+    <t>Trio</t>
+  </si>
+  <si>
+    <t>ACC4028</t>
+  </si>
+  <si>
+    <t>I. Allegro burlesco
+II. Lento espressivo
+III. Scherzo &amp; Trio
+IV. Finale: Allegro molto vivace</t>
+  </si>
+  <si>
+    <t>https://www.trevcomusic.com/cdn/shop/products/ACC4028Cover_1024x1024.jpeg?v=1571437378</t>
+  </si>
+  <si>
+    <t>https://www.trevcomusic.com/cdn/shop/products/ACC4028Page2_1024x1024.jpeg?v=1571437378</t>
+  </si>
+  <si>
+    <t>https://www.trevcomusic.com/cdn/shop/products/ACC4028Page1_1024x1024.jpeg?v=1571437378</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FWAnVap0u88?si=UuannNezQ0RA__4N</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Vsc_tf2BDgA?si=6I7TBqcExjfcT1AY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/nY4o1pE9nrQ?si=XHjma2-1DVRUO9Cx</t>
+  </si>
+  <si>
+    <t>https://youtu.be/s6abTKAlPXw?si=wP6rk7Lp3SR6f_Xd</t>
+  </si>
 </sst>
 </file>
 
@@ -18317,7 +18412,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m-d"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -18515,6 +18610,18 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -18548,7 +18655,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -18844,6 +18951,12 @@
     <xf borderId="0" fillId="3" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
@@ -76369,128 +76482,224 @@
       <c r="AI932" s="9"/>
     </row>
     <row r="933" ht="20.25" customHeight="1">
-      <c r="A933" s="5"/>
-      <c r="B933" s="5"/>
-      <c r="C933" s="5"/>
-      <c r="D933" s="5"/>
-      <c r="E933" s="99"/>
-      <c r="F933" s="99"/>
-      <c r="G933" s="5"/>
-      <c r="H933" s="5"/>
-      <c r="I933" s="5"/>
-      <c r="J933" s="5"/>
-      <c r="K933" s="100"/>
-      <c r="L933" s="5"/>
-      <c r="M933" s="5"/>
-      <c r="N933" s="5"/>
-      <c r="O933" s="5"/>
-      <c r="P933" s="5"/>
-      <c r="Q933" s="5"/>
-      <c r="R933" s="5"/>
-      <c r="S933" s="5"/>
-      <c r="T933" s="101"/>
-      <c r="U933" s="101"/>
-      <c r="V933" s="101"/>
-      <c r="W933" s="101"/>
-      <c r="X933" s="101"/>
-      <c r="Y933" s="101"/>
-      <c r="Z933" s="101"/>
-      <c r="AA933" s="101"/>
-      <c r="AB933" s="101"/>
-      <c r="AC933" s="101"/>
-      <c r="AD933" s="101"/>
-      <c r="AE933" s="101"/>
-      <c r="AF933" s="101"/>
-      <c r="AG933" s="101"/>
-      <c r="AH933" s="101"/>
-      <c r="AI933" s="101"/>
+      <c r="A933" s="31">
+        <v>6.0</v>
+      </c>
+      <c r="B933" s="17" t="s">
+        <v>5799</v>
+      </c>
+      <c r="C933" s="29" t="s">
+        <v>5800</v>
+      </c>
+      <c r="D933" s="15" t="s">
+        <v>4646</v>
+      </c>
+      <c r="E933" s="16" t="s">
+        <v>4647</v>
+      </c>
+      <c r="F933" s="49"/>
+      <c r="G933" s="33"/>
+      <c r="H933" s="18"/>
+      <c r="I933" s="18"/>
+      <c r="J933" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="K933" s="17" t="s">
+        <v>5801</v>
+      </c>
+      <c r="L933" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="M933" s="29" t="s">
+        <v>5802</v>
+      </c>
+      <c r="N933" s="18"/>
+      <c r="O933" s="33"/>
+      <c r="P933" s="33"/>
+      <c r="Q933" s="33"/>
+      <c r="R933" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="S933" s="99" t="s">
+        <v>5803</v>
+      </c>
+      <c r="T933" s="99" t="s">
+        <v>5804</v>
+      </c>
+      <c r="U933" s="97"/>
+      <c r="V933" s="97"/>
+      <c r="W933" s="97"/>
+      <c r="X933" s="97"/>
+      <c r="Y933" s="97"/>
+      <c r="Z933" s="97"/>
+      <c r="AA933" s="97"/>
+      <c r="AB933" s="18"/>
+      <c r="AC933" s="18"/>
+      <c r="AD933" s="18"/>
+      <c r="AE933" s="100" t="s">
+        <v>5805</v>
+      </c>
+      <c r="AF933" s="53" t="s">
+        <v>5806</v>
+      </c>
+      <c r="AG933" s="18"/>
+      <c r="AH933" s="18"/>
+      <c r="AI933" s="18"/>
     </row>
     <row r="934" ht="20.25" customHeight="1">
-      <c r="A934" s="5"/>
-      <c r="B934" s="5"/>
-      <c r="C934" s="5"/>
-      <c r="D934" s="5"/>
-      <c r="E934" s="99"/>
-      <c r="F934" s="99"/>
-      <c r="G934" s="5"/>
-      <c r="H934" s="5"/>
-      <c r="I934" s="5"/>
-      <c r="J934" s="5"/>
-      <c r="K934" s="100"/>
-      <c r="L934" s="5"/>
-      <c r="M934" s="5"/>
-      <c r="N934" s="5"/>
-      <c r="O934" s="5"/>
-      <c r="P934" s="5"/>
-      <c r="Q934" s="5"/>
-      <c r="R934" s="5"/>
-      <c r="S934" s="5"/>
-      <c r="T934" s="101"/>
-      <c r="U934" s="101"/>
-      <c r="V934" s="101"/>
-      <c r="W934" s="101"/>
-      <c r="X934" s="101"/>
-      <c r="Y934" s="101"/>
-      <c r="Z934" s="101"/>
-      <c r="AA934" s="101"/>
-      <c r="AB934" s="101"/>
-      <c r="AC934" s="101"/>
-      <c r="AD934" s="101"/>
-      <c r="AE934" s="101"/>
-      <c r="AF934" s="101"/>
-      <c r="AG934" s="101"/>
-      <c r="AH934" s="101"/>
-      <c r="AI934" s="101"/>
+      <c r="A934" s="31">
+        <v>2.0</v>
+      </c>
+      <c r="B934" s="10" t="s">
+        <v>5807</v>
+      </c>
+      <c r="C934" s="7" t="s">
+        <v>5808</v>
+      </c>
+      <c r="D934" s="6" t="s">
+        <v>4646</v>
+      </c>
+      <c r="E934" s="21" t="s">
+        <v>4647</v>
+      </c>
+      <c r="F934" s="8"/>
+      <c r="G934" s="11"/>
+      <c r="H934" s="9"/>
+      <c r="I934" s="9"/>
+      <c r="J934" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K934" s="10" t="s">
+        <v>5809</v>
+      </c>
+      <c r="L934" s="7">
+        <v>1999.0</v>
+      </c>
+      <c r="M934" s="11"/>
+      <c r="N934" s="9"/>
+      <c r="O934" s="11"/>
+      <c r="P934" s="7" t="s">
+        <v>5810</v>
+      </c>
+      <c r="Q934" s="7" t="s">
+        <v>5811</v>
+      </c>
+      <c r="R934" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="S934" s="60" t="s">
+        <v>5812</v>
+      </c>
+      <c r="T934" s="60" t="s">
+        <v>5813</v>
+      </c>
+      <c r="U934" s="95" t="s">
+        <v>5814</v>
+      </c>
+      <c r="V934" s="96"/>
+      <c r="W934" s="96"/>
+      <c r="X934" s="96"/>
+      <c r="Y934" s="96"/>
+      <c r="Z934" s="96"/>
+      <c r="AA934" s="96"/>
+      <c r="AB934" s="9"/>
+      <c r="AC934" s="9"/>
+      <c r="AD934" s="9"/>
+      <c r="AE934" s="74" t="s">
+        <v>5815</v>
+      </c>
+      <c r="AF934" s="50" t="s">
+        <v>5816</v>
+      </c>
+      <c r="AG934" s="50" t="s">
+        <v>5817</v>
+      </c>
+      <c r="AH934" s="9"/>
+      <c r="AI934" s="9"/>
     </row>
     <row r="935" ht="20.25" customHeight="1">
-      <c r="A935" s="5"/>
-      <c r="B935" s="5"/>
-      <c r="C935" s="5"/>
-      <c r="D935" s="5"/>
-      <c r="E935" s="99"/>
-      <c r="F935" s="99"/>
-      <c r="G935" s="5"/>
-      <c r="H935" s="5"/>
-      <c r="I935" s="5"/>
-      <c r="J935" s="5"/>
-      <c r="K935" s="100"/>
-      <c r="L935" s="5"/>
-      <c r="M935" s="5"/>
-      <c r="N935" s="5"/>
-      <c r="O935" s="5"/>
-      <c r="P935" s="5"/>
-      <c r="Q935" s="5"/>
-      <c r="R935" s="5"/>
-      <c r="S935" s="5"/>
-      <c r="T935" s="101"/>
-      <c r="U935" s="101"/>
-      <c r="V935" s="101"/>
-      <c r="W935" s="101"/>
-      <c r="X935" s="101"/>
-      <c r="Y935" s="101"/>
-      <c r="Z935" s="101"/>
-      <c r="AA935" s="101"/>
-      <c r="AB935" s="101"/>
-      <c r="AC935" s="101"/>
-      <c r="AD935" s="101"/>
-      <c r="AE935" s="101"/>
-      <c r="AF935" s="101"/>
-      <c r="AG935" s="101"/>
-      <c r="AH935" s="101"/>
-      <c r="AI935" s="101"/>
+      <c r="A935" s="31">
+        <v>3.0</v>
+      </c>
+      <c r="B935" s="17" t="s">
+        <v>5818</v>
+      </c>
+      <c r="C935" s="29" t="s">
+        <v>5819</v>
+      </c>
+      <c r="D935" s="15" t="s">
+        <v>4646</v>
+      </c>
+      <c r="E935" s="16" t="s">
+        <v>4647</v>
+      </c>
+      <c r="F935" s="49"/>
+      <c r="G935" s="33"/>
+      <c r="H935" s="18"/>
+      <c r="I935" s="18"/>
+      <c r="J935" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="K935" s="17" t="s">
+        <v>5820</v>
+      </c>
+      <c r="L935" s="29">
+        <v>2001.0</v>
+      </c>
+      <c r="M935" s="33"/>
+      <c r="N935" s="18"/>
+      <c r="O935" s="33"/>
+      <c r="P935" s="33"/>
+      <c r="Q935" s="29" t="s">
+        <v>5821</v>
+      </c>
+      <c r="R935" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="S935" s="78" t="s">
+        <v>5822</v>
+      </c>
+      <c r="T935" s="99" t="s">
+        <v>5823</v>
+      </c>
+      <c r="U935" s="99" t="s">
+        <v>5824</v>
+      </c>
+      <c r="V935" s="97"/>
+      <c r="W935" s="97"/>
+      <c r="X935" s="97"/>
+      <c r="Y935" s="97"/>
+      <c r="Z935" s="97"/>
+      <c r="AA935" s="97"/>
+      <c r="AB935" s="18"/>
+      <c r="AC935" s="18"/>
+      <c r="AD935" s="18"/>
+      <c r="AE935" s="25" t="s">
+        <v>5825</v>
+      </c>
+      <c r="AF935" s="53" t="s">
+        <v>5826</v>
+      </c>
+      <c r="AG935" s="53" t="s">
+        <v>5827</v>
+      </c>
+      <c r="AH935" s="53" t="s">
+        <v>5828</v>
+      </c>
+      <c r="AI935" s="18"/>
     </row>
     <row r="936" ht="20.25" customHeight="1">
       <c r="A936" s="5"/>
       <c r="B936" s="5"/>
       <c r="C936" s="5"/>
       <c r="D936" s="5"/>
-      <c r="E936" s="99"/>
-      <c r="F936" s="99"/>
+      <c r="E936" s="101"/>
+      <c r="F936" s="101"/>
       <c r="G936" s="5"/>
       <c r="H936" s="5"/>
       <c r="I936" s="5"/>
       <c r="J936" s="5"/>
-      <c r="K936" s="100"/>
+      <c r="K936" s="102"/>
       <c r="L936" s="5"/>
       <c r="M936" s="5"/>
       <c r="N936" s="5"/>
@@ -76499,35 +76708,35 @@
       <c r="Q936" s="5"/>
       <c r="R936" s="5"/>
       <c r="S936" s="5"/>
-      <c r="T936" s="101"/>
-      <c r="U936" s="101"/>
-      <c r="V936" s="101"/>
-      <c r="W936" s="101"/>
-      <c r="X936" s="101"/>
-      <c r="Y936" s="101"/>
-      <c r="Z936" s="101"/>
-      <c r="AA936" s="101"/>
-      <c r="AB936" s="101"/>
-      <c r="AC936" s="101"/>
-      <c r="AD936" s="101"/>
-      <c r="AE936" s="101"/>
-      <c r="AF936" s="101"/>
-      <c r="AG936" s="101"/>
-      <c r="AH936" s="101"/>
-      <c r="AI936" s="101"/>
+      <c r="T936" s="103"/>
+      <c r="U936" s="103"/>
+      <c r="V936" s="103"/>
+      <c r="W936" s="103"/>
+      <c r="X936" s="103"/>
+      <c r="Y936" s="103"/>
+      <c r="Z936" s="103"/>
+      <c r="AA936" s="103"/>
+      <c r="AB936" s="103"/>
+      <c r="AC936" s="103"/>
+      <c r="AD936" s="103"/>
+      <c r="AE936" s="103"/>
+      <c r="AF936" s="103"/>
+      <c r="AG936" s="103"/>
+      <c r="AH936" s="103"/>
+      <c r="AI936" s="103"/>
     </row>
     <row r="937" ht="20.25" customHeight="1">
       <c r="A937" s="5"/>
       <c r="B937" s="5"/>
       <c r="C937" s="5"/>
       <c r="D937" s="5"/>
-      <c r="E937" s="99"/>
-      <c r="F937" s="99"/>
+      <c r="E937" s="101"/>
+      <c r="F937" s="101"/>
       <c r="G937" s="5"/>
       <c r="H937" s="5"/>
       <c r="I937" s="5"/>
       <c r="J937" s="5"/>
-      <c r="K937" s="100"/>
+      <c r="K937" s="102"/>
       <c r="L937" s="5"/>
       <c r="M937" s="5"/>
       <c r="N937" s="5"/>
@@ -76536,35 +76745,35 @@
       <c r="Q937" s="5"/>
       <c r="R937" s="5"/>
       <c r="S937" s="5"/>
-      <c r="T937" s="101"/>
-      <c r="U937" s="101"/>
-      <c r="V937" s="101"/>
-      <c r="W937" s="101"/>
-      <c r="X937" s="101"/>
-      <c r="Y937" s="101"/>
-      <c r="Z937" s="101"/>
-      <c r="AA937" s="101"/>
-      <c r="AB937" s="101"/>
-      <c r="AC937" s="101"/>
-      <c r="AD937" s="101"/>
-      <c r="AE937" s="101"/>
-      <c r="AF937" s="101"/>
-      <c r="AG937" s="101"/>
-      <c r="AH937" s="101"/>
-      <c r="AI937" s="101"/>
+      <c r="T937" s="103"/>
+      <c r="U937" s="103"/>
+      <c r="V937" s="103"/>
+      <c r="W937" s="103"/>
+      <c r="X937" s="103"/>
+      <c r="Y937" s="103"/>
+      <c r="Z937" s="103"/>
+      <c r="AA937" s="103"/>
+      <c r="AB937" s="103"/>
+      <c r="AC937" s="103"/>
+      <c r="AD937" s="103"/>
+      <c r="AE937" s="103"/>
+      <c r="AF937" s="103"/>
+      <c r="AG937" s="103"/>
+      <c r="AH937" s="103"/>
+      <c r="AI937" s="103"/>
     </row>
     <row r="938" ht="20.25" customHeight="1">
       <c r="A938" s="5"/>
       <c r="B938" s="5"/>
       <c r="C938" s="5"/>
       <c r="D938" s="5"/>
-      <c r="E938" s="99"/>
-      <c r="F938" s="99"/>
+      <c r="E938" s="101"/>
+      <c r="F938" s="101"/>
       <c r="G938" s="5"/>
       <c r="H938" s="5"/>
       <c r="I938" s="5"/>
       <c r="J938" s="5"/>
-      <c r="K938" s="100"/>
+      <c r="K938" s="102"/>
       <c r="L938" s="5"/>
       <c r="M938" s="5"/>
       <c r="N938" s="5"/>
@@ -76573,35 +76782,35 @@
       <c r="Q938" s="5"/>
       <c r="R938" s="5"/>
       <c r="S938" s="5"/>
-      <c r="T938" s="101"/>
-      <c r="U938" s="101"/>
-      <c r="V938" s="101"/>
-      <c r="W938" s="101"/>
-      <c r="X938" s="101"/>
-      <c r="Y938" s="101"/>
-      <c r="Z938" s="101"/>
-      <c r="AA938" s="101"/>
-      <c r="AB938" s="101"/>
-      <c r="AC938" s="101"/>
-      <c r="AD938" s="101"/>
-      <c r="AE938" s="101"/>
-      <c r="AF938" s="101"/>
-      <c r="AG938" s="101"/>
-      <c r="AH938" s="101"/>
-      <c r="AI938" s="101"/>
+      <c r="T938" s="103"/>
+      <c r="U938" s="103"/>
+      <c r="V938" s="103"/>
+      <c r="W938" s="103"/>
+      <c r="X938" s="103"/>
+      <c r="Y938" s="103"/>
+      <c r="Z938" s="103"/>
+      <c r="AA938" s="103"/>
+      <c r="AB938" s="103"/>
+      <c r="AC938" s="103"/>
+      <c r="AD938" s="103"/>
+      <c r="AE938" s="103"/>
+      <c r="AF938" s="103"/>
+      <c r="AG938" s="103"/>
+      <c r="AH938" s="103"/>
+      <c r="AI938" s="103"/>
     </row>
     <row r="939" ht="20.25" customHeight="1">
       <c r="A939" s="5"/>
       <c r="B939" s="5"/>
       <c r="C939" s="5"/>
       <c r="D939" s="5"/>
-      <c r="E939" s="99"/>
-      <c r="F939" s="99"/>
+      <c r="E939" s="101"/>
+      <c r="F939" s="101"/>
       <c r="G939" s="5"/>
       <c r="H939" s="5"/>
       <c r="I939" s="5"/>
       <c r="J939" s="5"/>
-      <c r="K939" s="100"/>
+      <c r="K939" s="102"/>
       <c r="L939" s="5"/>
       <c r="M939" s="5"/>
       <c r="N939" s="5"/>
@@ -76610,35 +76819,35 @@
       <c r="Q939" s="5"/>
       <c r="R939" s="5"/>
       <c r="S939" s="5"/>
-      <c r="T939" s="101"/>
-      <c r="U939" s="101"/>
-      <c r="V939" s="101"/>
-      <c r="W939" s="101"/>
-      <c r="X939" s="101"/>
-      <c r="Y939" s="101"/>
-      <c r="Z939" s="101"/>
-      <c r="AA939" s="101"/>
-      <c r="AB939" s="101"/>
-      <c r="AC939" s="101"/>
-      <c r="AD939" s="101"/>
-      <c r="AE939" s="101"/>
-      <c r="AF939" s="101"/>
-      <c r="AG939" s="101"/>
-      <c r="AH939" s="101"/>
-      <c r="AI939" s="101"/>
+      <c r="T939" s="103"/>
+      <c r="U939" s="103"/>
+      <c r="V939" s="103"/>
+      <c r="W939" s="103"/>
+      <c r="X939" s="103"/>
+      <c r="Y939" s="103"/>
+      <c r="Z939" s="103"/>
+      <c r="AA939" s="103"/>
+      <c r="AB939" s="103"/>
+      <c r="AC939" s="103"/>
+      <c r="AD939" s="103"/>
+      <c r="AE939" s="103"/>
+      <c r="AF939" s="103"/>
+      <c r="AG939" s="103"/>
+      <c r="AH939" s="103"/>
+      <c r="AI939" s="103"/>
     </row>
     <row r="940" ht="20.25" customHeight="1">
       <c r="A940" s="5"/>
       <c r="B940" s="5"/>
       <c r="C940" s="5"/>
       <c r="D940" s="5"/>
-      <c r="E940" s="99"/>
-      <c r="F940" s="99"/>
+      <c r="E940" s="101"/>
+      <c r="F940" s="101"/>
       <c r="G940" s="5"/>
       <c r="H940" s="5"/>
       <c r="I940" s="5"/>
       <c r="J940" s="5"/>
-      <c r="K940" s="100"/>
+      <c r="K940" s="102"/>
       <c r="L940" s="5"/>
       <c r="M940" s="5"/>
       <c r="N940" s="5"/>
@@ -76647,35 +76856,35 @@
       <c r="Q940" s="5"/>
       <c r="R940" s="5"/>
       <c r="S940" s="5"/>
-      <c r="T940" s="101"/>
-      <c r="U940" s="101"/>
-      <c r="V940" s="101"/>
-      <c r="W940" s="101"/>
-      <c r="X940" s="101"/>
-      <c r="Y940" s="101"/>
-      <c r="Z940" s="101"/>
-      <c r="AA940" s="101"/>
-      <c r="AB940" s="101"/>
-      <c r="AC940" s="101"/>
-      <c r="AD940" s="101"/>
-      <c r="AE940" s="101"/>
-      <c r="AF940" s="101"/>
-      <c r="AG940" s="101"/>
-      <c r="AH940" s="101"/>
-      <c r="AI940" s="101"/>
+      <c r="T940" s="103"/>
+      <c r="U940" s="103"/>
+      <c r="V940" s="103"/>
+      <c r="W940" s="103"/>
+      <c r="X940" s="103"/>
+      <c r="Y940" s="103"/>
+      <c r="Z940" s="103"/>
+      <c r="AA940" s="103"/>
+      <c r="AB940" s="103"/>
+      <c r="AC940" s="103"/>
+      <c r="AD940" s="103"/>
+      <c r="AE940" s="103"/>
+      <c r="AF940" s="103"/>
+      <c r="AG940" s="103"/>
+      <c r="AH940" s="103"/>
+      <c r="AI940" s="103"/>
     </row>
     <row r="941" ht="20.25" customHeight="1">
       <c r="A941" s="5"/>
       <c r="B941" s="5"/>
       <c r="C941" s="5"/>
       <c r="D941" s="5"/>
-      <c r="E941" s="99"/>
-      <c r="F941" s="99"/>
+      <c r="E941" s="101"/>
+      <c r="F941" s="101"/>
       <c r="G941" s="5"/>
       <c r="H941" s="5"/>
       <c r="I941" s="5"/>
       <c r="J941" s="5"/>
-      <c r="K941" s="100"/>
+      <c r="K941" s="102"/>
       <c r="L941" s="5"/>
       <c r="M941" s="5"/>
       <c r="N941" s="5"/>
@@ -76684,35 +76893,35 @@
       <c r="Q941" s="5"/>
       <c r="R941" s="5"/>
       <c r="S941" s="5"/>
-      <c r="T941" s="101"/>
-      <c r="U941" s="101"/>
-      <c r="V941" s="101"/>
-      <c r="W941" s="101"/>
-      <c r="X941" s="101"/>
-      <c r="Y941" s="101"/>
-      <c r="Z941" s="101"/>
-      <c r="AA941" s="101"/>
-      <c r="AB941" s="101"/>
-      <c r="AC941" s="101"/>
-      <c r="AD941" s="101"/>
-      <c r="AE941" s="101"/>
-      <c r="AF941" s="101"/>
-      <c r="AG941" s="101"/>
-      <c r="AH941" s="101"/>
-      <c r="AI941" s="101"/>
+      <c r="T941" s="103"/>
+      <c r="U941" s="103"/>
+      <c r="V941" s="103"/>
+      <c r="W941" s="103"/>
+      <c r="X941" s="103"/>
+      <c r="Y941" s="103"/>
+      <c r="Z941" s="103"/>
+      <c r="AA941" s="103"/>
+      <c r="AB941" s="103"/>
+      <c r="AC941" s="103"/>
+      <c r="AD941" s="103"/>
+      <c r="AE941" s="103"/>
+      <c r="AF941" s="103"/>
+      <c r="AG941" s="103"/>
+      <c r="AH941" s="103"/>
+      <c r="AI941" s="103"/>
     </row>
     <row r="942" ht="20.25" customHeight="1">
       <c r="A942" s="5"/>
       <c r="B942" s="5"/>
       <c r="C942" s="5"/>
       <c r="D942" s="5"/>
-      <c r="E942" s="99"/>
-      <c r="F942" s="99"/>
+      <c r="E942" s="101"/>
+      <c r="F942" s="101"/>
       <c r="G942" s="5"/>
       <c r="H942" s="5"/>
       <c r="I942" s="5"/>
       <c r="J942" s="5"/>
-      <c r="K942" s="100"/>
+      <c r="K942" s="102"/>
       <c r="L942" s="5"/>
       <c r="M942" s="5"/>
       <c r="N942" s="5"/>
@@ -76721,35 +76930,35 @@
       <c r="Q942" s="5"/>
       <c r="R942" s="5"/>
       <c r="S942" s="5"/>
-      <c r="T942" s="101"/>
-      <c r="U942" s="101"/>
-      <c r="V942" s="101"/>
-      <c r="W942" s="101"/>
-      <c r="X942" s="101"/>
-      <c r="Y942" s="101"/>
-      <c r="Z942" s="101"/>
-      <c r="AA942" s="101"/>
-      <c r="AB942" s="101"/>
-      <c r="AC942" s="101"/>
-      <c r="AD942" s="101"/>
-      <c r="AE942" s="101"/>
-      <c r="AF942" s="101"/>
-      <c r="AG942" s="101"/>
-      <c r="AH942" s="101"/>
-      <c r="AI942" s="101"/>
+      <c r="T942" s="103"/>
+      <c r="U942" s="103"/>
+      <c r="V942" s="103"/>
+      <c r="W942" s="103"/>
+      <c r="X942" s="103"/>
+      <c r="Y942" s="103"/>
+      <c r="Z942" s="103"/>
+      <c r="AA942" s="103"/>
+      <c r="AB942" s="103"/>
+      <c r="AC942" s="103"/>
+      <c r="AD942" s="103"/>
+      <c r="AE942" s="103"/>
+      <c r="AF942" s="103"/>
+      <c r="AG942" s="103"/>
+      <c r="AH942" s="103"/>
+      <c r="AI942" s="103"/>
     </row>
     <row r="943" ht="20.25" customHeight="1">
       <c r="A943" s="5"/>
       <c r="B943" s="5"/>
       <c r="C943" s="5"/>
       <c r="D943" s="5"/>
-      <c r="E943" s="99"/>
-      <c r="F943" s="99"/>
+      <c r="E943" s="101"/>
+      <c r="F943" s="101"/>
       <c r="G943" s="5"/>
       <c r="H943" s="5"/>
       <c r="I943" s="5"/>
       <c r="J943" s="5"/>
-      <c r="K943" s="100"/>
+      <c r="K943" s="102"/>
       <c r="L943" s="5"/>
       <c r="M943" s="5"/>
       <c r="N943" s="5"/>
@@ -76758,35 +76967,35 @@
       <c r="Q943" s="5"/>
       <c r="R943" s="5"/>
       <c r="S943" s="5"/>
-      <c r="T943" s="101"/>
-      <c r="U943" s="101"/>
-      <c r="V943" s="101"/>
-      <c r="W943" s="101"/>
-      <c r="X943" s="101"/>
-      <c r="Y943" s="101"/>
-      <c r="Z943" s="101"/>
-      <c r="AA943" s="101"/>
-      <c r="AB943" s="101"/>
-      <c r="AC943" s="101"/>
-      <c r="AD943" s="101"/>
-      <c r="AE943" s="101"/>
-      <c r="AF943" s="101"/>
-      <c r="AG943" s="101"/>
-      <c r="AH943" s="101"/>
-      <c r="AI943" s="101"/>
+      <c r="T943" s="103"/>
+      <c r="U943" s="103"/>
+      <c r="V943" s="103"/>
+      <c r="W943" s="103"/>
+      <c r="X943" s="103"/>
+      <c r="Y943" s="103"/>
+      <c r="Z943" s="103"/>
+      <c r="AA943" s="103"/>
+      <c r="AB943" s="103"/>
+      <c r="AC943" s="103"/>
+      <c r="AD943" s="103"/>
+      <c r="AE943" s="103"/>
+      <c r="AF943" s="103"/>
+      <c r="AG943" s="103"/>
+      <c r="AH943" s="103"/>
+      <c r="AI943" s="103"/>
     </row>
     <row r="944" ht="20.25" customHeight="1">
       <c r="A944" s="5"/>
       <c r="B944" s="5"/>
       <c r="C944" s="5"/>
       <c r="D944" s="5"/>
-      <c r="E944" s="99"/>
-      <c r="F944" s="99"/>
+      <c r="E944" s="101"/>
+      <c r="F944" s="101"/>
       <c r="G944" s="5"/>
       <c r="H944" s="5"/>
       <c r="I944" s="5"/>
       <c r="J944" s="5"/>
-      <c r="K944" s="100"/>
+      <c r="K944" s="102"/>
       <c r="L944" s="5"/>
       <c r="M944" s="5"/>
       <c r="N944" s="5"/>
@@ -76795,35 +77004,35 @@
       <c r="Q944" s="5"/>
       <c r="R944" s="5"/>
       <c r="S944" s="5"/>
-      <c r="T944" s="101"/>
-      <c r="U944" s="101"/>
-      <c r="V944" s="101"/>
-      <c r="W944" s="101"/>
-      <c r="X944" s="101"/>
-      <c r="Y944" s="101"/>
-      <c r="Z944" s="101"/>
-      <c r="AA944" s="101"/>
-      <c r="AB944" s="101"/>
-      <c r="AC944" s="101"/>
-      <c r="AD944" s="101"/>
-      <c r="AE944" s="101"/>
-      <c r="AF944" s="101"/>
-      <c r="AG944" s="101"/>
-      <c r="AH944" s="101"/>
-      <c r="AI944" s="101"/>
+      <c r="T944" s="103"/>
+      <c r="U944" s="103"/>
+      <c r="V944" s="103"/>
+      <c r="W944" s="103"/>
+      <c r="X944" s="103"/>
+      <c r="Y944" s="103"/>
+      <c r="Z944" s="103"/>
+      <c r="AA944" s="103"/>
+      <c r="AB944" s="103"/>
+      <c r="AC944" s="103"/>
+      <c r="AD944" s="103"/>
+      <c r="AE944" s="103"/>
+      <c r="AF944" s="103"/>
+      <c r="AG944" s="103"/>
+      <c r="AH944" s="103"/>
+      <c r="AI944" s="103"/>
     </row>
     <row r="945" ht="20.25" customHeight="1">
       <c r="A945" s="5"/>
       <c r="B945" s="5"/>
       <c r="C945" s="5"/>
       <c r="D945" s="5"/>
-      <c r="E945" s="99"/>
-      <c r="F945" s="99"/>
+      <c r="E945" s="101"/>
+      <c r="F945" s="101"/>
       <c r="G945" s="5"/>
       <c r="H945" s="5"/>
       <c r="I945" s="5"/>
       <c r="J945" s="5"/>
-      <c r="K945" s="100"/>
+      <c r="K945" s="102"/>
       <c r="L945" s="5"/>
       <c r="M945" s="5"/>
       <c r="N945" s="5"/>
@@ -76832,35 +77041,35 @@
       <c r="Q945" s="5"/>
       <c r="R945" s="5"/>
       <c r="S945" s="5"/>
-      <c r="T945" s="101"/>
-      <c r="U945" s="101"/>
-      <c r="V945" s="101"/>
-      <c r="W945" s="101"/>
-      <c r="X945" s="101"/>
-      <c r="Y945" s="101"/>
-      <c r="Z945" s="101"/>
-      <c r="AA945" s="101"/>
-      <c r="AB945" s="101"/>
-      <c r="AC945" s="101"/>
-      <c r="AD945" s="101"/>
-      <c r="AE945" s="101"/>
-      <c r="AF945" s="101"/>
-      <c r="AG945" s="101"/>
-      <c r="AH945" s="101"/>
-      <c r="AI945" s="101"/>
+      <c r="T945" s="103"/>
+      <c r="U945" s="103"/>
+      <c r="V945" s="103"/>
+      <c r="W945" s="103"/>
+      <c r="X945" s="103"/>
+      <c r="Y945" s="103"/>
+      <c r="Z945" s="103"/>
+      <c r="AA945" s="103"/>
+      <c r="AB945" s="103"/>
+      <c r="AC945" s="103"/>
+      <c r="AD945" s="103"/>
+      <c r="AE945" s="103"/>
+      <c r="AF945" s="103"/>
+      <c r="AG945" s="103"/>
+      <c r="AH945" s="103"/>
+      <c r="AI945" s="103"/>
     </row>
     <row r="946" ht="20.25" customHeight="1">
       <c r="A946" s="5"/>
       <c r="B946" s="5"/>
       <c r="C946" s="5"/>
       <c r="D946" s="5"/>
-      <c r="E946" s="99"/>
-      <c r="F946" s="99"/>
+      <c r="E946" s="101"/>
+      <c r="F946" s="101"/>
       <c r="G946" s="5"/>
       <c r="H946" s="5"/>
       <c r="I946" s="5"/>
       <c r="J946" s="5"/>
-      <c r="K946" s="100"/>
+      <c r="K946" s="102"/>
       <c r="L946" s="5"/>
       <c r="M946" s="5"/>
       <c r="N946" s="5"/>
@@ -76869,35 +77078,35 @@
       <c r="Q946" s="5"/>
       <c r="R946" s="5"/>
       <c r="S946" s="5"/>
-      <c r="T946" s="101"/>
-      <c r="U946" s="101"/>
-      <c r="V946" s="101"/>
-      <c r="W946" s="101"/>
-      <c r="X946" s="101"/>
-      <c r="Y946" s="101"/>
-      <c r="Z946" s="101"/>
-      <c r="AA946" s="101"/>
-      <c r="AB946" s="101"/>
-      <c r="AC946" s="101"/>
-      <c r="AD946" s="101"/>
-      <c r="AE946" s="101"/>
-      <c r="AF946" s="101"/>
-      <c r="AG946" s="101"/>
-      <c r="AH946" s="101"/>
-      <c r="AI946" s="101"/>
+      <c r="T946" s="103"/>
+      <c r="U946" s="103"/>
+      <c r="V946" s="103"/>
+      <c r="W946" s="103"/>
+      <c r="X946" s="103"/>
+      <c r="Y946" s="103"/>
+      <c r="Z946" s="103"/>
+      <c r="AA946" s="103"/>
+      <c r="AB946" s="103"/>
+      <c r="AC946" s="103"/>
+      <c r="AD946" s="103"/>
+      <c r="AE946" s="103"/>
+      <c r="AF946" s="103"/>
+      <c r="AG946" s="103"/>
+      <c r="AH946" s="103"/>
+      <c r="AI946" s="103"/>
     </row>
     <row r="947" ht="20.25" customHeight="1">
       <c r="A947" s="5"/>
       <c r="B947" s="5"/>
       <c r="C947" s="5"/>
       <c r="D947" s="5"/>
-      <c r="E947" s="99"/>
-      <c r="F947" s="99"/>
+      <c r="E947" s="101"/>
+      <c r="F947" s="101"/>
       <c r="G947" s="5"/>
       <c r="H947" s="5"/>
       <c r="I947" s="5"/>
       <c r="J947" s="5"/>
-      <c r="K947" s="100"/>
+      <c r="K947" s="102"/>
       <c r="L947" s="5"/>
       <c r="M947" s="5"/>
       <c r="N947" s="5"/>
@@ -76906,35 +77115,35 @@
       <c r="Q947" s="5"/>
       <c r="R947" s="5"/>
       <c r="S947" s="5"/>
-      <c r="T947" s="101"/>
-      <c r="U947" s="101"/>
-      <c r="V947" s="101"/>
-      <c r="W947" s="101"/>
-      <c r="X947" s="101"/>
-      <c r="Y947" s="101"/>
-      <c r="Z947" s="101"/>
-      <c r="AA947" s="101"/>
-      <c r="AB947" s="101"/>
-      <c r="AC947" s="101"/>
-      <c r="AD947" s="101"/>
-      <c r="AE947" s="101"/>
-      <c r="AF947" s="101"/>
-      <c r="AG947" s="101"/>
-      <c r="AH947" s="101"/>
-      <c r="AI947" s="101"/>
+      <c r="T947" s="103"/>
+      <c r="U947" s="103"/>
+      <c r="V947" s="103"/>
+      <c r="W947" s="103"/>
+      <c r="X947" s="103"/>
+      <c r="Y947" s="103"/>
+      <c r="Z947" s="103"/>
+      <c r="AA947" s="103"/>
+      <c r="AB947" s="103"/>
+      <c r="AC947" s="103"/>
+      <c r="AD947" s="103"/>
+      <c r="AE947" s="103"/>
+      <c r="AF947" s="103"/>
+      <c r="AG947" s="103"/>
+      <c r="AH947" s="103"/>
+      <c r="AI947" s="103"/>
     </row>
     <row r="948" ht="20.25" customHeight="1">
       <c r="A948" s="5"/>
       <c r="B948" s="5"/>
       <c r="C948" s="5"/>
       <c r="D948" s="5"/>
-      <c r="E948" s="99"/>
-      <c r="F948" s="99"/>
+      <c r="E948" s="101"/>
+      <c r="F948" s="101"/>
       <c r="G948" s="5"/>
       <c r="H948" s="5"/>
       <c r="I948" s="5"/>
       <c r="J948" s="5"/>
-      <c r="K948" s="100"/>
+      <c r="K948" s="102"/>
       <c r="L948" s="5"/>
       <c r="M948" s="5"/>
       <c r="N948" s="5"/>
@@ -76943,35 +77152,35 @@
       <c r="Q948" s="5"/>
       <c r="R948" s="5"/>
       <c r="S948" s="5"/>
-      <c r="T948" s="101"/>
-      <c r="U948" s="101"/>
-      <c r="V948" s="101"/>
-      <c r="W948" s="101"/>
-      <c r="X948" s="101"/>
-      <c r="Y948" s="101"/>
-      <c r="Z948" s="101"/>
-      <c r="AA948" s="101"/>
-      <c r="AB948" s="101"/>
-      <c r="AC948" s="101"/>
-      <c r="AD948" s="101"/>
-      <c r="AE948" s="101"/>
-      <c r="AF948" s="101"/>
-      <c r="AG948" s="101"/>
-      <c r="AH948" s="101"/>
-      <c r="AI948" s="101"/>
+      <c r="T948" s="103"/>
+      <c r="U948" s="103"/>
+      <c r="V948" s="103"/>
+      <c r="W948" s="103"/>
+      <c r="X948" s="103"/>
+      <c r="Y948" s="103"/>
+      <c r="Z948" s="103"/>
+      <c r="AA948" s="103"/>
+      <c r="AB948" s="103"/>
+      <c r="AC948" s="103"/>
+      <c r="AD948" s="103"/>
+      <c r="AE948" s="103"/>
+      <c r="AF948" s="103"/>
+      <c r="AG948" s="103"/>
+      <c r="AH948" s="103"/>
+      <c r="AI948" s="103"/>
     </row>
     <row r="949" ht="20.25" customHeight="1">
       <c r="A949" s="5"/>
       <c r="B949" s="5"/>
       <c r="C949" s="5"/>
       <c r="D949" s="5"/>
-      <c r="E949" s="99"/>
-      <c r="F949" s="99"/>
+      <c r="E949" s="101"/>
+      <c r="F949" s="101"/>
       <c r="G949" s="5"/>
       <c r="H949" s="5"/>
       <c r="I949" s="5"/>
       <c r="J949" s="5"/>
-      <c r="K949" s="100"/>
+      <c r="K949" s="102"/>
       <c r="L949" s="5"/>
       <c r="M949" s="5"/>
       <c r="N949" s="5"/>
@@ -76980,35 +77189,35 @@
       <c r="Q949" s="5"/>
       <c r="R949" s="5"/>
       <c r="S949" s="5"/>
-      <c r="T949" s="101"/>
-      <c r="U949" s="101"/>
-      <c r="V949" s="101"/>
-      <c r="W949" s="101"/>
-      <c r="X949" s="101"/>
-      <c r="Y949" s="101"/>
-      <c r="Z949" s="101"/>
-      <c r="AA949" s="101"/>
-      <c r="AB949" s="101"/>
-      <c r="AC949" s="101"/>
-      <c r="AD949" s="101"/>
-      <c r="AE949" s="101"/>
-      <c r="AF949" s="101"/>
-      <c r="AG949" s="101"/>
-      <c r="AH949" s="101"/>
-      <c r="AI949" s="101"/>
+      <c r="T949" s="103"/>
+      <c r="U949" s="103"/>
+      <c r="V949" s="103"/>
+      <c r="W949" s="103"/>
+      <c r="X949" s="103"/>
+      <c r="Y949" s="103"/>
+      <c r="Z949" s="103"/>
+      <c r="AA949" s="103"/>
+      <c r="AB949" s="103"/>
+      <c r="AC949" s="103"/>
+      <c r="AD949" s="103"/>
+      <c r="AE949" s="103"/>
+      <c r="AF949" s="103"/>
+      <c r="AG949" s="103"/>
+      <c r="AH949" s="103"/>
+      <c r="AI949" s="103"/>
     </row>
     <row r="950" ht="20.25" customHeight="1">
       <c r="A950" s="5"/>
       <c r="B950" s="5"/>
       <c r="C950" s="5"/>
       <c r="D950" s="5"/>
-      <c r="E950" s="99"/>
-      <c r="F950" s="99"/>
+      <c r="E950" s="101"/>
+      <c r="F950" s="101"/>
       <c r="G950" s="5"/>
       <c r="H950" s="5"/>
       <c r="I950" s="5"/>
       <c r="J950" s="5"/>
-      <c r="K950" s="100"/>
+      <c r="K950" s="102"/>
       <c r="L950" s="5"/>
       <c r="M950" s="5"/>
       <c r="N950" s="5"/>
@@ -77017,35 +77226,35 @@
       <c r="Q950" s="5"/>
       <c r="R950" s="5"/>
       <c r="S950" s="5"/>
-      <c r="T950" s="101"/>
-      <c r="U950" s="101"/>
-      <c r="V950" s="101"/>
-      <c r="W950" s="101"/>
-      <c r="X950" s="101"/>
-      <c r="Y950" s="101"/>
-      <c r="Z950" s="101"/>
-      <c r="AA950" s="101"/>
-      <c r="AB950" s="101"/>
-      <c r="AC950" s="101"/>
-      <c r="AD950" s="101"/>
-      <c r="AE950" s="101"/>
-      <c r="AF950" s="101"/>
-      <c r="AG950" s="101"/>
-      <c r="AH950" s="101"/>
-      <c r="AI950" s="101"/>
+      <c r="T950" s="103"/>
+      <c r="U950" s="103"/>
+      <c r="V950" s="103"/>
+      <c r="W950" s="103"/>
+      <c r="X950" s="103"/>
+      <c r="Y950" s="103"/>
+      <c r="Z950" s="103"/>
+      <c r="AA950" s="103"/>
+      <c r="AB950" s="103"/>
+      <c r="AC950" s="103"/>
+      <c r="AD950" s="103"/>
+      <c r="AE950" s="103"/>
+      <c r="AF950" s="103"/>
+      <c r="AG950" s="103"/>
+      <c r="AH950" s="103"/>
+      <c r="AI950" s="103"/>
     </row>
     <row r="951" ht="20.25" customHeight="1">
       <c r="A951" s="5"/>
       <c r="B951" s="5"/>
       <c r="C951" s="5"/>
       <c r="D951" s="5"/>
-      <c r="E951" s="99"/>
-      <c r="F951" s="99"/>
+      <c r="E951" s="101"/>
+      <c r="F951" s="101"/>
       <c r="G951" s="5"/>
       <c r="H951" s="5"/>
       <c r="I951" s="5"/>
       <c r="J951" s="5"/>
-      <c r="K951" s="100"/>
+      <c r="K951" s="102"/>
       <c r="L951" s="5"/>
       <c r="M951" s="5"/>
       <c r="N951" s="5"/>
@@ -77054,35 +77263,35 @@
       <c r="Q951" s="5"/>
       <c r="R951" s="5"/>
       <c r="S951" s="5"/>
-      <c r="T951" s="101"/>
-      <c r="U951" s="101"/>
-      <c r="V951" s="101"/>
-      <c r="W951" s="101"/>
-      <c r="X951" s="101"/>
-      <c r="Y951" s="101"/>
-      <c r="Z951" s="101"/>
-      <c r="AA951" s="101"/>
-      <c r="AB951" s="101"/>
-      <c r="AC951" s="101"/>
-      <c r="AD951" s="101"/>
-      <c r="AE951" s="101"/>
-      <c r="AF951" s="101"/>
-      <c r="AG951" s="101"/>
-      <c r="AH951" s="101"/>
-      <c r="AI951" s="101"/>
+      <c r="T951" s="103"/>
+      <c r="U951" s="103"/>
+      <c r="V951" s="103"/>
+      <c r="W951" s="103"/>
+      <c r="X951" s="103"/>
+      <c r="Y951" s="103"/>
+      <c r="Z951" s="103"/>
+      <c r="AA951" s="103"/>
+      <c r="AB951" s="103"/>
+      <c r="AC951" s="103"/>
+      <c r="AD951" s="103"/>
+      <c r="AE951" s="103"/>
+      <c r="AF951" s="103"/>
+      <c r="AG951" s="103"/>
+      <c r="AH951" s="103"/>
+      <c r="AI951" s="103"/>
     </row>
     <row r="952" ht="20.25" customHeight="1">
       <c r="A952" s="5"/>
       <c r="B952" s="5"/>
       <c r="C952" s="5"/>
       <c r="D952" s="5"/>
-      <c r="E952" s="99"/>
-      <c r="F952" s="99"/>
+      <c r="E952" s="101"/>
+      <c r="F952" s="101"/>
       <c r="G952" s="5"/>
       <c r="H952" s="5"/>
       <c r="I952" s="5"/>
       <c r="J952" s="5"/>
-      <c r="K952" s="100"/>
+      <c r="K952" s="102"/>
       <c r="L952" s="5"/>
       <c r="M952" s="5"/>
       <c r="N952" s="5"/>
@@ -77091,35 +77300,35 @@
       <c r="Q952" s="5"/>
       <c r="R952" s="5"/>
       <c r="S952" s="5"/>
-      <c r="T952" s="101"/>
-      <c r="U952" s="101"/>
-      <c r="V952" s="101"/>
-      <c r="W952" s="101"/>
-      <c r="X952" s="101"/>
-      <c r="Y952" s="101"/>
-      <c r="Z952" s="101"/>
-      <c r="AA952" s="101"/>
-      <c r="AB952" s="101"/>
-      <c r="AC952" s="101"/>
-      <c r="AD952" s="101"/>
-      <c r="AE952" s="101"/>
-      <c r="AF952" s="101"/>
-      <c r="AG952" s="101"/>
-      <c r="AH952" s="101"/>
-      <c r="AI952" s="101"/>
+      <c r="T952" s="103"/>
+      <c r="U952" s="103"/>
+      <c r="V952" s="103"/>
+      <c r="W952" s="103"/>
+      <c r="X952" s="103"/>
+      <c r="Y952" s="103"/>
+      <c r="Z952" s="103"/>
+      <c r="AA952" s="103"/>
+      <c r="AB952" s="103"/>
+      <c r="AC952" s="103"/>
+      <c r="AD952" s="103"/>
+      <c r="AE952" s="103"/>
+      <c r="AF952" s="103"/>
+      <c r="AG952" s="103"/>
+      <c r="AH952" s="103"/>
+      <c r="AI952" s="103"/>
     </row>
     <row r="953" ht="20.25" customHeight="1">
       <c r="A953" s="5"/>
       <c r="B953" s="5"/>
       <c r="C953" s="5"/>
       <c r="D953" s="5"/>
-      <c r="E953" s="99"/>
-      <c r="F953" s="99"/>
+      <c r="E953" s="101"/>
+      <c r="F953" s="101"/>
       <c r="G953" s="5"/>
       <c r="H953" s="5"/>
       <c r="I953" s="5"/>
       <c r="J953" s="5"/>
-      <c r="K953" s="100"/>
+      <c r="K953" s="102"/>
       <c r="L953" s="5"/>
       <c r="M953" s="5"/>
       <c r="N953" s="5"/>
@@ -77128,35 +77337,35 @@
       <c r="Q953" s="5"/>
       <c r="R953" s="5"/>
       <c r="S953" s="5"/>
-      <c r="T953" s="101"/>
-      <c r="U953" s="101"/>
-      <c r="V953" s="101"/>
-      <c r="W953" s="101"/>
-      <c r="X953" s="101"/>
-      <c r="Y953" s="101"/>
-      <c r="Z953" s="101"/>
-      <c r="AA953" s="101"/>
-      <c r="AB953" s="101"/>
-      <c r="AC953" s="101"/>
-      <c r="AD953" s="101"/>
-      <c r="AE953" s="101"/>
-      <c r="AF953" s="101"/>
-      <c r="AG953" s="101"/>
-      <c r="AH953" s="101"/>
-      <c r="AI953" s="101"/>
+      <c r="T953" s="103"/>
+      <c r="U953" s="103"/>
+      <c r="V953" s="103"/>
+      <c r="W953" s="103"/>
+      <c r="X953" s="103"/>
+      <c r="Y953" s="103"/>
+      <c r="Z953" s="103"/>
+      <c r="AA953" s="103"/>
+      <c r="AB953" s="103"/>
+      <c r="AC953" s="103"/>
+      <c r="AD953" s="103"/>
+      <c r="AE953" s="103"/>
+      <c r="AF953" s="103"/>
+      <c r="AG953" s="103"/>
+      <c r="AH953" s="103"/>
+      <c r="AI953" s="103"/>
     </row>
     <row r="954" ht="20.25" customHeight="1">
       <c r="A954" s="5"/>
       <c r="B954" s="5"/>
       <c r="C954" s="5"/>
       <c r="D954" s="5"/>
-      <c r="E954" s="99"/>
-      <c r="F954" s="99"/>
+      <c r="E954" s="101"/>
+      <c r="F954" s="101"/>
       <c r="G954" s="5"/>
       <c r="H954" s="5"/>
       <c r="I954" s="5"/>
       <c r="J954" s="5"/>
-      <c r="K954" s="100"/>
+      <c r="K954" s="102"/>
       <c r="L954" s="5"/>
       <c r="M954" s="5"/>
       <c r="N954" s="5"/>
@@ -77165,35 +77374,35 @@
       <c r="Q954" s="5"/>
       <c r="R954" s="5"/>
       <c r="S954" s="5"/>
-      <c r="T954" s="101"/>
-      <c r="U954" s="101"/>
-      <c r="V954" s="101"/>
-      <c r="W954" s="101"/>
-      <c r="X954" s="101"/>
-      <c r="Y954" s="101"/>
-      <c r="Z954" s="101"/>
-      <c r="AA954" s="101"/>
-      <c r="AB954" s="101"/>
-      <c r="AC954" s="101"/>
-      <c r="AD954" s="101"/>
-      <c r="AE954" s="101"/>
-      <c r="AF954" s="101"/>
-      <c r="AG954" s="101"/>
-      <c r="AH954" s="101"/>
-      <c r="AI954" s="101"/>
+      <c r="T954" s="103"/>
+      <c r="U954" s="103"/>
+      <c r="V954" s="103"/>
+      <c r="W954" s="103"/>
+      <c r="X954" s="103"/>
+      <c r="Y954" s="103"/>
+      <c r="Z954" s="103"/>
+      <c r="AA954" s="103"/>
+      <c r="AB954" s="103"/>
+      <c r="AC954" s="103"/>
+      <c r="AD954" s="103"/>
+      <c r="AE954" s="103"/>
+      <c r="AF954" s="103"/>
+      <c r="AG954" s="103"/>
+      <c r="AH954" s="103"/>
+      <c r="AI954" s="103"/>
     </row>
     <row r="955" ht="20.25" customHeight="1">
       <c r="A955" s="5"/>
       <c r="B955" s="5"/>
       <c r="C955" s="5"/>
       <c r="D955" s="5"/>
-      <c r="E955" s="99"/>
-      <c r="F955" s="99"/>
+      <c r="E955" s="101"/>
+      <c r="F955" s="101"/>
       <c r="G955" s="5"/>
       <c r="H955" s="5"/>
       <c r="I955" s="5"/>
       <c r="J955" s="5"/>
-      <c r="K955" s="100"/>
+      <c r="K955" s="102"/>
       <c r="L955" s="5"/>
       <c r="M955" s="5"/>
       <c r="N955" s="5"/>
@@ -77202,35 +77411,35 @@
       <c r="Q955" s="5"/>
       <c r="R955" s="5"/>
       <c r="S955" s="5"/>
-      <c r="T955" s="101"/>
-      <c r="U955" s="101"/>
-      <c r="V955" s="101"/>
-      <c r="W955" s="101"/>
-      <c r="X955" s="101"/>
-      <c r="Y955" s="101"/>
-      <c r="Z955" s="101"/>
-      <c r="AA955" s="101"/>
-      <c r="AB955" s="101"/>
-      <c r="AC955" s="101"/>
-      <c r="AD955" s="101"/>
-      <c r="AE955" s="101"/>
-      <c r="AF955" s="101"/>
-      <c r="AG955" s="101"/>
-      <c r="AH955" s="101"/>
-      <c r="AI955" s="101"/>
+      <c r="T955" s="103"/>
+      <c r="U955" s="103"/>
+      <c r="V955" s="103"/>
+      <c r="W955" s="103"/>
+      <c r="X955" s="103"/>
+      <c r="Y955" s="103"/>
+      <c r="Z955" s="103"/>
+      <c r="AA955" s="103"/>
+      <c r="AB955" s="103"/>
+      <c r="AC955" s="103"/>
+      <c r="AD955" s="103"/>
+      <c r="AE955" s="103"/>
+      <c r="AF955" s="103"/>
+      <c r="AG955" s="103"/>
+      <c r="AH955" s="103"/>
+      <c r="AI955" s="103"/>
     </row>
     <row r="956" ht="20.25" customHeight="1">
       <c r="A956" s="5"/>
       <c r="B956" s="5"/>
       <c r="C956" s="5"/>
       <c r="D956" s="5"/>
-      <c r="E956" s="99"/>
-      <c r="F956" s="99"/>
+      <c r="E956" s="101"/>
+      <c r="F956" s="101"/>
       <c r="G956" s="5"/>
       <c r="H956" s="5"/>
       <c r="I956" s="5"/>
       <c r="J956" s="5"/>
-      <c r="K956" s="100"/>
+      <c r="K956" s="102"/>
       <c r="L956" s="5"/>
       <c r="M956" s="5"/>
       <c r="N956" s="5"/>
@@ -77239,35 +77448,35 @@
       <c r="Q956" s="5"/>
       <c r="R956" s="5"/>
       <c r="S956" s="5"/>
-      <c r="T956" s="101"/>
-      <c r="U956" s="101"/>
-      <c r="V956" s="101"/>
-      <c r="W956" s="101"/>
-      <c r="X956" s="101"/>
-      <c r="Y956" s="101"/>
-      <c r="Z956" s="101"/>
-      <c r="AA956" s="101"/>
-      <c r="AB956" s="101"/>
-      <c r="AC956" s="101"/>
-      <c r="AD956" s="101"/>
-      <c r="AE956" s="101"/>
-      <c r="AF956" s="101"/>
-      <c r="AG956" s="101"/>
-      <c r="AH956" s="101"/>
-      <c r="AI956" s="101"/>
+      <c r="T956" s="103"/>
+      <c r="U956" s="103"/>
+      <c r="V956" s="103"/>
+      <c r="W956" s="103"/>
+      <c r="X956" s="103"/>
+      <c r="Y956" s="103"/>
+      <c r="Z956" s="103"/>
+      <c r="AA956" s="103"/>
+      <c r="AB956" s="103"/>
+      <c r="AC956" s="103"/>
+      <c r="AD956" s="103"/>
+      <c r="AE956" s="103"/>
+      <c r="AF956" s="103"/>
+      <c r="AG956" s="103"/>
+      <c r="AH956" s="103"/>
+      <c r="AI956" s="103"/>
     </row>
     <row r="957" ht="20.25" customHeight="1">
       <c r="A957" s="5"/>
       <c r="B957" s="5"/>
       <c r="C957" s="5"/>
       <c r="D957" s="5"/>
-      <c r="E957" s="99"/>
-      <c r="F957" s="99"/>
+      <c r="E957" s="101"/>
+      <c r="F957" s="101"/>
       <c r="G957" s="5"/>
       <c r="H957" s="5"/>
       <c r="I957" s="5"/>
       <c r="J957" s="5"/>
-      <c r="K957" s="100"/>
+      <c r="K957" s="102"/>
       <c r="L957" s="5"/>
       <c r="M957" s="5"/>
       <c r="N957" s="5"/>
@@ -77276,35 +77485,35 @@
       <c r="Q957" s="5"/>
       <c r="R957" s="5"/>
       <c r="S957" s="5"/>
-      <c r="T957" s="101"/>
-      <c r="U957" s="101"/>
-      <c r="V957" s="101"/>
-      <c r="W957" s="101"/>
-      <c r="X957" s="101"/>
-      <c r="Y957" s="101"/>
-      <c r="Z957" s="101"/>
-      <c r="AA957" s="101"/>
-      <c r="AB957" s="101"/>
-      <c r="AC957" s="101"/>
-      <c r="AD957" s="101"/>
-      <c r="AE957" s="101"/>
-      <c r="AF957" s="101"/>
-      <c r="AG957" s="101"/>
-      <c r="AH957" s="101"/>
-      <c r="AI957" s="101"/>
+      <c r="T957" s="103"/>
+      <c r="U957" s="103"/>
+      <c r="V957" s="103"/>
+      <c r="W957" s="103"/>
+      <c r="X957" s="103"/>
+      <c r="Y957" s="103"/>
+      <c r="Z957" s="103"/>
+      <c r="AA957" s="103"/>
+      <c r="AB957" s="103"/>
+      <c r="AC957" s="103"/>
+      <c r="AD957" s="103"/>
+      <c r="AE957" s="103"/>
+      <c r="AF957" s="103"/>
+      <c r="AG957" s="103"/>
+      <c r="AH957" s="103"/>
+      <c r="AI957" s="103"/>
     </row>
     <row r="958" ht="20.25" customHeight="1">
       <c r="A958" s="5"/>
       <c r="B958" s="5"/>
       <c r="C958" s="5"/>
       <c r="D958" s="5"/>
-      <c r="E958" s="99"/>
-      <c r="F958" s="99"/>
+      <c r="E958" s="101"/>
+      <c r="F958" s="101"/>
       <c r="G958" s="5"/>
       <c r="H958" s="5"/>
       <c r="I958" s="5"/>
       <c r="J958" s="5"/>
-      <c r="K958" s="100"/>
+      <c r="K958" s="102"/>
       <c r="L958" s="5"/>
       <c r="M958" s="5"/>
       <c r="N958" s="5"/>
@@ -77313,35 +77522,35 @@
       <c r="Q958" s="5"/>
       <c r="R958" s="5"/>
       <c r="S958" s="5"/>
-      <c r="T958" s="101"/>
-      <c r="U958" s="101"/>
-      <c r="V958" s="101"/>
-      <c r="W958" s="101"/>
-      <c r="X958" s="101"/>
-      <c r="Y958" s="101"/>
-      <c r="Z958" s="101"/>
-      <c r="AA958" s="101"/>
-      <c r="AB958" s="101"/>
-      <c r="AC958" s="101"/>
-      <c r="AD958" s="101"/>
-      <c r="AE958" s="101"/>
-      <c r="AF958" s="101"/>
-      <c r="AG958" s="101"/>
-      <c r="AH958" s="101"/>
-      <c r="AI958" s="101"/>
+      <c r="T958" s="103"/>
+      <c r="U958" s="103"/>
+      <c r="V958" s="103"/>
+      <c r="W958" s="103"/>
+      <c r="X958" s="103"/>
+      <c r="Y958" s="103"/>
+      <c r="Z958" s="103"/>
+      <c r="AA958" s="103"/>
+      <c r="AB958" s="103"/>
+      <c r="AC958" s="103"/>
+      <c r="AD958" s="103"/>
+      <c r="AE958" s="103"/>
+      <c r="AF958" s="103"/>
+      <c r="AG958" s="103"/>
+      <c r="AH958" s="103"/>
+      <c r="AI958" s="103"/>
     </row>
     <row r="959" ht="20.25" customHeight="1">
       <c r="A959" s="5"/>
       <c r="B959" s="5"/>
       <c r="C959" s="5"/>
       <c r="D959" s="5"/>
-      <c r="E959" s="99"/>
-      <c r="F959" s="99"/>
+      <c r="E959" s="101"/>
+      <c r="F959" s="101"/>
       <c r="G959" s="5"/>
       <c r="H959" s="5"/>
       <c r="I959" s="5"/>
       <c r="J959" s="5"/>
-      <c r="K959" s="100"/>
+      <c r="K959" s="102"/>
       <c r="L959" s="5"/>
       <c r="M959" s="5"/>
       <c r="N959" s="5"/>
@@ -77350,35 +77559,35 @@
       <c r="Q959" s="5"/>
       <c r="R959" s="5"/>
       <c r="S959" s="5"/>
-      <c r="T959" s="101"/>
-      <c r="U959" s="101"/>
-      <c r="V959" s="101"/>
-      <c r="W959" s="101"/>
-      <c r="X959" s="101"/>
-      <c r="Y959" s="101"/>
-      <c r="Z959" s="101"/>
-      <c r="AA959" s="101"/>
-      <c r="AB959" s="101"/>
-      <c r="AC959" s="101"/>
-      <c r="AD959" s="101"/>
-      <c r="AE959" s="101"/>
-      <c r="AF959" s="101"/>
-      <c r="AG959" s="101"/>
-      <c r="AH959" s="101"/>
-      <c r="AI959" s="101"/>
+      <c r="T959" s="103"/>
+      <c r="U959" s="103"/>
+      <c r="V959" s="103"/>
+      <c r="W959" s="103"/>
+      <c r="X959" s="103"/>
+      <c r="Y959" s="103"/>
+      <c r="Z959" s="103"/>
+      <c r="AA959" s="103"/>
+      <c r="AB959" s="103"/>
+      <c r="AC959" s="103"/>
+      <c r="AD959" s="103"/>
+      <c r="AE959" s="103"/>
+      <c r="AF959" s="103"/>
+      <c r="AG959" s="103"/>
+      <c r="AH959" s="103"/>
+      <c r="AI959" s="103"/>
     </row>
     <row r="960" ht="20.25" customHeight="1">
       <c r="A960" s="5"/>
       <c r="B960" s="5"/>
       <c r="C960" s="5"/>
       <c r="D960" s="5"/>
-      <c r="E960" s="99"/>
-      <c r="F960" s="99"/>
+      <c r="E960" s="101"/>
+      <c r="F960" s="101"/>
       <c r="G960" s="5"/>
       <c r="H960" s="5"/>
       <c r="I960" s="5"/>
       <c r="J960" s="5"/>
-      <c r="K960" s="100"/>
+      <c r="K960" s="102"/>
       <c r="L960" s="5"/>
       <c r="M960" s="5"/>
       <c r="N960" s="5"/>
@@ -77387,35 +77596,35 @@
       <c r="Q960" s="5"/>
       <c r="R960" s="5"/>
       <c r="S960" s="5"/>
-      <c r="T960" s="101"/>
-      <c r="U960" s="101"/>
-      <c r="V960" s="101"/>
-      <c r="W960" s="101"/>
-      <c r="X960" s="101"/>
-      <c r="Y960" s="101"/>
-      <c r="Z960" s="101"/>
-      <c r="AA960" s="101"/>
-      <c r="AB960" s="101"/>
-      <c r="AC960" s="101"/>
-      <c r="AD960" s="101"/>
-      <c r="AE960" s="101"/>
-      <c r="AF960" s="101"/>
-      <c r="AG960" s="101"/>
-      <c r="AH960" s="101"/>
-      <c r="AI960" s="101"/>
+      <c r="T960" s="103"/>
+      <c r="U960" s="103"/>
+      <c r="V960" s="103"/>
+      <c r="W960" s="103"/>
+      <c r="X960" s="103"/>
+      <c r="Y960" s="103"/>
+      <c r="Z960" s="103"/>
+      <c r="AA960" s="103"/>
+      <c r="AB960" s="103"/>
+      <c r="AC960" s="103"/>
+      <c r="AD960" s="103"/>
+      <c r="AE960" s="103"/>
+      <c r="AF960" s="103"/>
+      <c r="AG960" s="103"/>
+      <c r="AH960" s="103"/>
+      <c r="AI960" s="103"/>
     </row>
     <row r="961" ht="20.25" customHeight="1">
       <c r="A961" s="5"/>
       <c r="B961" s="5"/>
       <c r="C961" s="5"/>
       <c r="D961" s="5"/>
-      <c r="E961" s="99"/>
-      <c r="F961" s="99"/>
+      <c r="E961" s="101"/>
+      <c r="F961" s="101"/>
       <c r="G961" s="5"/>
       <c r="H961" s="5"/>
       <c r="I961" s="5"/>
       <c r="J961" s="5"/>
-      <c r="K961" s="100"/>
+      <c r="K961" s="102"/>
       <c r="L961" s="5"/>
       <c r="M961" s="5"/>
       <c r="N961" s="5"/>
@@ -77424,35 +77633,35 @@
       <c r="Q961" s="5"/>
       <c r="R961" s="5"/>
       <c r="S961" s="5"/>
-      <c r="T961" s="101"/>
-      <c r="U961" s="101"/>
-      <c r="V961" s="101"/>
-      <c r="W961" s="101"/>
-      <c r="X961" s="101"/>
-      <c r="Y961" s="101"/>
-      <c r="Z961" s="101"/>
-      <c r="AA961" s="101"/>
-      <c r="AB961" s="101"/>
-      <c r="AC961" s="101"/>
-      <c r="AD961" s="101"/>
-      <c r="AE961" s="101"/>
-      <c r="AF961" s="101"/>
-      <c r="AG961" s="101"/>
-      <c r="AH961" s="101"/>
-      <c r="AI961" s="101"/>
+      <c r="T961" s="103"/>
+      <c r="U961" s="103"/>
+      <c r="V961" s="103"/>
+      <c r="W961" s="103"/>
+      <c r="X961" s="103"/>
+      <c r="Y961" s="103"/>
+      <c r="Z961" s="103"/>
+      <c r="AA961" s="103"/>
+      <c r="AB961" s="103"/>
+      <c r="AC961" s="103"/>
+      <c r="AD961" s="103"/>
+      <c r="AE961" s="103"/>
+      <c r="AF961" s="103"/>
+      <c r="AG961" s="103"/>
+      <c r="AH961" s="103"/>
+      <c r="AI961" s="103"/>
     </row>
     <row r="962" ht="20.25" customHeight="1">
       <c r="A962" s="5"/>
       <c r="B962" s="5"/>
       <c r="C962" s="5"/>
       <c r="D962" s="5"/>
-      <c r="E962" s="99"/>
-      <c r="F962" s="99"/>
+      <c r="E962" s="101"/>
+      <c r="F962" s="101"/>
       <c r="G962" s="5"/>
       <c r="H962" s="5"/>
       <c r="I962" s="5"/>
       <c r="J962" s="5"/>
-      <c r="K962" s="100"/>
+      <c r="K962" s="102"/>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
       <c r="N962" s="5"/>
@@ -77461,35 +77670,35 @@
       <c r="Q962" s="5"/>
       <c r="R962" s="5"/>
       <c r="S962" s="5"/>
-      <c r="T962" s="101"/>
-      <c r="U962" s="101"/>
-      <c r="V962" s="101"/>
-      <c r="W962" s="101"/>
-      <c r="X962" s="101"/>
-      <c r="Y962" s="101"/>
-      <c r="Z962" s="101"/>
-      <c r="AA962" s="101"/>
-      <c r="AB962" s="101"/>
-      <c r="AC962" s="101"/>
-      <c r="AD962" s="101"/>
-      <c r="AE962" s="101"/>
-      <c r="AF962" s="101"/>
-      <c r="AG962" s="101"/>
-      <c r="AH962" s="101"/>
-      <c r="AI962" s="101"/>
+      <c r="T962" s="103"/>
+      <c r="U962" s="103"/>
+      <c r="V962" s="103"/>
+      <c r="W962" s="103"/>
+      <c r="X962" s="103"/>
+      <c r="Y962" s="103"/>
+      <c r="Z962" s="103"/>
+      <c r="AA962" s="103"/>
+      <c r="AB962" s="103"/>
+      <c r="AC962" s="103"/>
+      <c r="AD962" s="103"/>
+      <c r="AE962" s="103"/>
+      <c r="AF962" s="103"/>
+      <c r="AG962" s="103"/>
+      <c r="AH962" s="103"/>
+      <c r="AI962" s="103"/>
     </row>
     <row r="963" ht="20.25" customHeight="1">
       <c r="A963" s="5"/>
       <c r="B963" s="5"/>
       <c r="C963" s="5"/>
       <c r="D963" s="5"/>
-      <c r="E963" s="99"/>
-      <c r="F963" s="99"/>
+      <c r="E963" s="101"/>
+      <c r="F963" s="101"/>
       <c r="G963" s="5"/>
       <c r="H963" s="5"/>
       <c r="I963" s="5"/>
       <c r="J963" s="5"/>
-      <c r="K963" s="100"/>
+      <c r="K963" s="102"/>
       <c r="L963" s="5"/>
       <c r="M963" s="5"/>
       <c r="N963" s="5"/>
@@ -77498,35 +77707,35 @@
       <c r="Q963" s="5"/>
       <c r="R963" s="5"/>
       <c r="S963" s="5"/>
-      <c r="T963" s="101"/>
-      <c r="U963" s="101"/>
-      <c r="V963" s="101"/>
-      <c r="W963" s="101"/>
-      <c r="X963" s="101"/>
-      <c r="Y963" s="101"/>
-      <c r="Z963" s="101"/>
-      <c r="AA963" s="101"/>
-      <c r="AB963" s="101"/>
-      <c r="AC963" s="101"/>
-      <c r="AD963" s="101"/>
-      <c r="AE963" s="101"/>
-      <c r="AF963" s="101"/>
-      <c r="AG963" s="101"/>
-      <c r="AH963" s="101"/>
-      <c r="AI963" s="101"/>
+      <c r="T963" s="103"/>
+      <c r="U963" s="103"/>
+      <c r="V963" s="103"/>
+      <c r="W963" s="103"/>
+      <c r="X963" s="103"/>
+      <c r="Y963" s="103"/>
+      <c r="Z963" s="103"/>
+      <c r="AA963" s="103"/>
+      <c r="AB963" s="103"/>
+      <c r="AC963" s="103"/>
+      <c r="AD963" s="103"/>
+      <c r="AE963" s="103"/>
+      <c r="AF963" s="103"/>
+      <c r="AG963" s="103"/>
+      <c r="AH963" s="103"/>
+      <c r="AI963" s="103"/>
     </row>
     <row r="964" ht="20.25" customHeight="1">
       <c r="A964" s="5"/>
       <c r="B964" s="5"/>
       <c r="C964" s="5"/>
       <c r="D964" s="5"/>
-      <c r="E964" s="99"/>
-      <c r="F964" s="99"/>
+      <c r="E964" s="101"/>
+      <c r="F964" s="101"/>
       <c r="G964" s="5"/>
       <c r="H964" s="5"/>
       <c r="I964" s="5"/>
       <c r="J964" s="5"/>
-      <c r="K964" s="100"/>
+      <c r="K964" s="102"/>
       <c r="L964" s="5"/>
       <c r="M964" s="5"/>
       <c r="N964" s="5"/>
@@ -77535,35 +77744,35 @@
       <c r="Q964" s="5"/>
       <c r="R964" s="5"/>
       <c r="S964" s="5"/>
-      <c r="T964" s="101"/>
-      <c r="U964" s="101"/>
-      <c r="V964" s="101"/>
-      <c r="W964" s="101"/>
-      <c r="X964" s="101"/>
-      <c r="Y964" s="101"/>
-      <c r="Z964" s="101"/>
-      <c r="AA964" s="101"/>
-      <c r="AB964" s="101"/>
-      <c r="AC964" s="101"/>
-      <c r="AD964" s="101"/>
-      <c r="AE964" s="101"/>
-      <c r="AF964" s="101"/>
-      <c r="AG964" s="101"/>
-      <c r="AH964" s="101"/>
-      <c r="AI964" s="101"/>
+      <c r="T964" s="103"/>
+      <c r="U964" s="103"/>
+      <c r="V964" s="103"/>
+      <c r="W964" s="103"/>
+      <c r="X964" s="103"/>
+      <c r="Y964" s="103"/>
+      <c r="Z964" s="103"/>
+      <c r="AA964" s="103"/>
+      <c r="AB964" s="103"/>
+      <c r="AC964" s="103"/>
+      <c r="AD964" s="103"/>
+      <c r="AE964" s="103"/>
+      <c r="AF964" s="103"/>
+      <c r="AG964" s="103"/>
+      <c r="AH964" s="103"/>
+      <c r="AI964" s="103"/>
     </row>
     <row r="965" ht="20.25" customHeight="1">
       <c r="A965" s="5"/>
       <c r="B965" s="5"/>
       <c r="C965" s="5"/>
       <c r="D965" s="5"/>
-      <c r="E965" s="99"/>
-      <c r="F965" s="99"/>
+      <c r="E965" s="101"/>
+      <c r="F965" s="101"/>
       <c r="G965" s="5"/>
       <c r="H965" s="5"/>
       <c r="I965" s="5"/>
       <c r="J965" s="5"/>
-      <c r="K965" s="100"/>
+      <c r="K965" s="102"/>
       <c r="L965" s="5"/>
       <c r="M965" s="5"/>
       <c r="N965" s="5"/>
@@ -77572,35 +77781,35 @@
       <c r="Q965" s="5"/>
       <c r="R965" s="5"/>
       <c r="S965" s="5"/>
-      <c r="T965" s="101"/>
-      <c r="U965" s="101"/>
-      <c r="V965" s="101"/>
-      <c r="W965" s="101"/>
-      <c r="X965" s="101"/>
-      <c r="Y965" s="101"/>
-      <c r="Z965" s="101"/>
-      <c r="AA965" s="101"/>
-      <c r="AB965" s="101"/>
-      <c r="AC965" s="101"/>
-      <c r="AD965" s="101"/>
-      <c r="AE965" s="101"/>
-      <c r="AF965" s="101"/>
-      <c r="AG965" s="101"/>
-      <c r="AH965" s="101"/>
-      <c r="AI965" s="101"/>
+      <c r="T965" s="103"/>
+      <c r="U965" s="103"/>
+      <c r="V965" s="103"/>
+      <c r="W965" s="103"/>
+      <c r="X965" s="103"/>
+      <c r="Y965" s="103"/>
+      <c r="Z965" s="103"/>
+      <c r="AA965" s="103"/>
+      <c r="AB965" s="103"/>
+      <c r="AC965" s="103"/>
+      <c r="AD965" s="103"/>
+      <c r="AE965" s="103"/>
+      <c r="AF965" s="103"/>
+      <c r="AG965" s="103"/>
+      <c r="AH965" s="103"/>
+      <c r="AI965" s="103"/>
     </row>
     <row r="966" ht="20.25" customHeight="1">
       <c r="A966" s="5"/>
       <c r="B966" s="5"/>
       <c r="C966" s="5"/>
       <c r="D966" s="5"/>
-      <c r="E966" s="99"/>
-      <c r="F966" s="99"/>
+      <c r="E966" s="101"/>
+      <c r="F966" s="101"/>
       <c r="G966" s="5"/>
       <c r="H966" s="5"/>
       <c r="I966" s="5"/>
       <c r="J966" s="5"/>
-      <c r="K966" s="100"/>
+      <c r="K966" s="102"/>
       <c r="L966" s="5"/>
       <c r="M966" s="5"/>
       <c r="N966" s="5"/>
@@ -77609,35 +77818,35 @@
       <c r="Q966" s="5"/>
       <c r="R966" s="5"/>
       <c r="S966" s="5"/>
-      <c r="T966" s="101"/>
-      <c r="U966" s="101"/>
-      <c r="V966" s="101"/>
-      <c r="W966" s="101"/>
-      <c r="X966" s="101"/>
-      <c r="Y966" s="101"/>
-      <c r="Z966" s="101"/>
-      <c r="AA966" s="101"/>
-      <c r="AB966" s="101"/>
-      <c r="AC966" s="101"/>
-      <c r="AD966" s="101"/>
-      <c r="AE966" s="101"/>
-      <c r="AF966" s="101"/>
-      <c r="AG966" s="101"/>
-      <c r="AH966" s="101"/>
-      <c r="AI966" s="101"/>
+      <c r="T966" s="103"/>
+      <c r="U966" s="103"/>
+      <c r="V966" s="103"/>
+      <c r="W966" s="103"/>
+      <c r="X966" s="103"/>
+      <c r="Y966" s="103"/>
+      <c r="Z966" s="103"/>
+      <c r="AA966" s="103"/>
+      <c r="AB966" s="103"/>
+      <c r="AC966" s="103"/>
+      <c r="AD966" s="103"/>
+      <c r="AE966" s="103"/>
+      <c r="AF966" s="103"/>
+      <c r="AG966" s="103"/>
+      <c r="AH966" s="103"/>
+      <c r="AI966" s="103"/>
     </row>
     <row r="967" ht="20.25" customHeight="1">
       <c r="A967" s="5"/>
       <c r="B967" s="5"/>
       <c r="C967" s="5"/>
       <c r="D967" s="5"/>
-      <c r="E967" s="99"/>
-      <c r="F967" s="99"/>
+      <c r="E967" s="101"/>
+      <c r="F967" s="101"/>
       <c r="G967" s="5"/>
       <c r="H967" s="5"/>
       <c r="I967" s="5"/>
       <c r="J967" s="5"/>
-      <c r="K967" s="100"/>
+      <c r="K967" s="102"/>
       <c r="L967" s="5"/>
       <c r="M967" s="5"/>
       <c r="N967" s="5"/>
@@ -77646,35 +77855,35 @@
       <c r="Q967" s="5"/>
       <c r="R967" s="5"/>
       <c r="S967" s="5"/>
-      <c r="T967" s="101"/>
-      <c r="U967" s="101"/>
-      <c r="V967" s="101"/>
-      <c r="W967" s="101"/>
-      <c r="X967" s="101"/>
-      <c r="Y967" s="101"/>
-      <c r="Z967" s="101"/>
-      <c r="AA967" s="101"/>
-      <c r="AB967" s="101"/>
-      <c r="AC967" s="101"/>
-      <c r="AD967" s="101"/>
-      <c r="AE967" s="101"/>
-      <c r="AF967" s="101"/>
-      <c r="AG967" s="101"/>
-      <c r="AH967" s="101"/>
-      <c r="AI967" s="101"/>
+      <c r="T967" s="103"/>
+      <c r="U967" s="103"/>
+      <c r="V967" s="103"/>
+      <c r="W967" s="103"/>
+      <c r="X967" s="103"/>
+      <c r="Y967" s="103"/>
+      <c r="Z967" s="103"/>
+      <c r="AA967" s="103"/>
+      <c r="AB967" s="103"/>
+      <c r="AC967" s="103"/>
+      <c r="AD967" s="103"/>
+      <c r="AE967" s="103"/>
+      <c r="AF967" s="103"/>
+      <c r="AG967" s="103"/>
+      <c r="AH967" s="103"/>
+      <c r="AI967" s="103"/>
     </row>
     <row r="968" ht="20.25" customHeight="1">
       <c r="A968" s="5"/>
       <c r="B968" s="5"/>
       <c r="C968" s="5"/>
       <c r="D968" s="5"/>
-      <c r="E968" s="99"/>
-      <c r="F968" s="99"/>
+      <c r="E968" s="101"/>
+      <c r="F968" s="101"/>
       <c r="G968" s="5"/>
       <c r="H968" s="5"/>
       <c r="I968" s="5"/>
       <c r="J968" s="5"/>
-      <c r="K968" s="100"/>
+      <c r="K968" s="102"/>
       <c r="L968" s="5"/>
       <c r="M968" s="5"/>
       <c r="N968" s="5"/>
@@ -77683,35 +77892,35 @@
       <c r="Q968" s="5"/>
       <c r="R968" s="5"/>
       <c r="S968" s="5"/>
-      <c r="T968" s="101"/>
-      <c r="U968" s="101"/>
-      <c r="V968" s="101"/>
-      <c r="W968" s="101"/>
-      <c r="X968" s="101"/>
-      <c r="Y968" s="101"/>
-      <c r="Z968" s="101"/>
-      <c r="AA968" s="101"/>
-      <c r="AB968" s="101"/>
-      <c r="AC968" s="101"/>
-      <c r="AD968" s="101"/>
-      <c r="AE968" s="101"/>
-      <c r="AF968" s="101"/>
-      <c r="AG968" s="101"/>
-      <c r="AH968" s="101"/>
-      <c r="AI968" s="101"/>
+      <c r="T968" s="103"/>
+      <c r="U968" s="103"/>
+      <c r="V968" s="103"/>
+      <c r="W968" s="103"/>
+      <c r="X968" s="103"/>
+      <c r="Y968" s="103"/>
+      <c r="Z968" s="103"/>
+      <c r="AA968" s="103"/>
+      <c r="AB968" s="103"/>
+      <c r="AC968" s="103"/>
+      <c r="AD968" s="103"/>
+      <c r="AE968" s="103"/>
+      <c r="AF968" s="103"/>
+      <c r="AG968" s="103"/>
+      <c r="AH968" s="103"/>
+      <c r="AI968" s="103"/>
     </row>
     <row r="969" ht="20.25" customHeight="1">
       <c r="A969" s="5"/>
       <c r="B969" s="5"/>
       <c r="C969" s="5"/>
       <c r="D969" s="5"/>
-      <c r="E969" s="99"/>
-      <c r="F969" s="99"/>
+      <c r="E969" s="101"/>
+      <c r="F969" s="101"/>
       <c r="G969" s="5"/>
       <c r="H969" s="5"/>
       <c r="I969" s="5"/>
       <c r="J969" s="5"/>
-      <c r="K969" s="100"/>
+      <c r="K969" s="102"/>
       <c r="L969" s="5"/>
       <c r="M969" s="5"/>
       <c r="N969" s="5"/>
@@ -77720,35 +77929,35 @@
       <c r="Q969" s="5"/>
       <c r="R969" s="5"/>
       <c r="S969" s="5"/>
-      <c r="T969" s="101"/>
-      <c r="U969" s="101"/>
-      <c r="V969" s="101"/>
-      <c r="W969" s="101"/>
-      <c r="X969" s="101"/>
-      <c r="Y969" s="101"/>
-      <c r="Z969" s="101"/>
-      <c r="AA969" s="101"/>
-      <c r="AB969" s="101"/>
-      <c r="AC969" s="101"/>
-      <c r="AD969" s="101"/>
-      <c r="AE969" s="101"/>
-      <c r="AF969" s="101"/>
-      <c r="AG969" s="101"/>
-      <c r="AH969" s="101"/>
-      <c r="AI969" s="101"/>
+      <c r="T969" s="103"/>
+      <c r="U969" s="103"/>
+      <c r="V969" s="103"/>
+      <c r="W969" s="103"/>
+      <c r="X969" s="103"/>
+      <c r="Y969" s="103"/>
+      <c r="Z969" s="103"/>
+      <c r="AA969" s="103"/>
+      <c r="AB969" s="103"/>
+      <c r="AC969" s="103"/>
+      <c r="AD969" s="103"/>
+      <c r="AE969" s="103"/>
+      <c r="AF969" s="103"/>
+      <c r="AG969" s="103"/>
+      <c r="AH969" s="103"/>
+      <c r="AI969" s="103"/>
     </row>
     <row r="970" ht="20.25" customHeight="1">
       <c r="A970" s="5"/>
       <c r="B970" s="5"/>
       <c r="C970" s="5"/>
       <c r="D970" s="5"/>
-      <c r="E970" s="99"/>
-      <c r="F970" s="99"/>
+      <c r="E970" s="101"/>
+      <c r="F970" s="101"/>
       <c r="G970" s="5"/>
       <c r="H970" s="5"/>
       <c r="I970" s="5"/>
       <c r="J970" s="5"/>
-      <c r="K970" s="100"/>
+      <c r="K970" s="102"/>
       <c r="L970" s="5"/>
       <c r="M970" s="5"/>
       <c r="N970" s="5"/>
@@ -77757,35 +77966,35 @@
       <c r="Q970" s="5"/>
       <c r="R970" s="5"/>
       <c r="S970" s="5"/>
-      <c r="T970" s="101"/>
-      <c r="U970" s="101"/>
-      <c r="V970" s="101"/>
-      <c r="W970" s="101"/>
-      <c r="X970" s="101"/>
-      <c r="Y970" s="101"/>
-      <c r="Z970" s="101"/>
-      <c r="AA970" s="101"/>
-      <c r="AB970" s="101"/>
-      <c r="AC970" s="101"/>
-      <c r="AD970" s="101"/>
-      <c r="AE970" s="101"/>
-      <c r="AF970" s="101"/>
-      <c r="AG970" s="101"/>
-      <c r="AH970" s="101"/>
-      <c r="AI970" s="101"/>
+      <c r="T970" s="103"/>
+      <c r="U970" s="103"/>
+      <c r="V970" s="103"/>
+      <c r="W970" s="103"/>
+      <c r="X970" s="103"/>
+      <c r="Y970" s="103"/>
+      <c r="Z970" s="103"/>
+      <c r="AA970" s="103"/>
+      <c r="AB970" s="103"/>
+      <c r="AC970" s="103"/>
+      <c r="AD970" s="103"/>
+      <c r="AE970" s="103"/>
+      <c r="AF970" s="103"/>
+      <c r="AG970" s="103"/>
+      <c r="AH970" s="103"/>
+      <c r="AI970" s="103"/>
     </row>
     <row r="971" ht="20.25" customHeight="1">
       <c r="A971" s="5"/>
       <c r="B971" s="5"/>
       <c r="C971" s="5"/>
       <c r="D971" s="5"/>
-      <c r="E971" s="99"/>
-      <c r="F971" s="99"/>
+      <c r="E971" s="101"/>
+      <c r="F971" s="101"/>
       <c r="G971" s="5"/>
       <c r="H971" s="5"/>
       <c r="I971" s="5"/>
       <c r="J971" s="5"/>
-      <c r="K971" s="100"/>
+      <c r="K971" s="102"/>
       <c r="L971" s="5"/>
       <c r="M971" s="5"/>
       <c r="N971" s="5"/>
@@ -77794,35 +78003,35 @@
       <c r="Q971" s="5"/>
       <c r="R971" s="5"/>
       <c r="S971" s="5"/>
-      <c r="T971" s="101"/>
-      <c r="U971" s="101"/>
-      <c r="V971" s="101"/>
-      <c r="W971" s="101"/>
-      <c r="X971" s="101"/>
-      <c r="Y971" s="101"/>
-      <c r="Z971" s="101"/>
-      <c r="AA971" s="101"/>
-      <c r="AB971" s="101"/>
-      <c r="AC971" s="101"/>
-      <c r="AD971" s="101"/>
-      <c r="AE971" s="101"/>
-      <c r="AF971" s="101"/>
-      <c r="AG971" s="101"/>
-      <c r="AH971" s="101"/>
-      <c r="AI971" s="101"/>
+      <c r="T971" s="103"/>
+      <c r="U971" s="103"/>
+      <c r="V971" s="103"/>
+      <c r="W971" s="103"/>
+      <c r="X971" s="103"/>
+      <c r="Y971" s="103"/>
+      <c r="Z971" s="103"/>
+      <c r="AA971" s="103"/>
+      <c r="AB971" s="103"/>
+      <c r="AC971" s="103"/>
+      <c r="AD971" s="103"/>
+      <c r="AE971" s="103"/>
+      <c r="AF971" s="103"/>
+      <c r="AG971" s="103"/>
+      <c r="AH971" s="103"/>
+      <c r="AI971" s="103"/>
     </row>
     <row r="972" ht="20.25" customHeight="1">
       <c r="A972" s="5"/>
       <c r="B972" s="5"/>
       <c r="C972" s="5"/>
       <c r="D972" s="5"/>
-      <c r="E972" s="99"/>
-      <c r="F972" s="99"/>
+      <c r="E972" s="101"/>
+      <c r="F972" s="101"/>
       <c r="G972" s="5"/>
       <c r="H972" s="5"/>
       <c r="I972" s="5"/>
       <c r="J972" s="5"/>
-      <c r="K972" s="100"/>
+      <c r="K972" s="102"/>
       <c r="L972" s="5"/>
       <c r="M972" s="5"/>
       <c r="N972" s="5"/>
@@ -77831,35 +78040,35 @@
       <c r="Q972" s="5"/>
       <c r="R972" s="5"/>
       <c r="S972" s="5"/>
-      <c r="T972" s="101"/>
-      <c r="U972" s="101"/>
-      <c r="V972" s="101"/>
-      <c r="W972" s="101"/>
-      <c r="X972" s="101"/>
-      <c r="Y972" s="101"/>
-      <c r="Z972" s="101"/>
-      <c r="AA972" s="101"/>
-      <c r="AB972" s="101"/>
-      <c r="AC972" s="101"/>
-      <c r="AD972" s="101"/>
-      <c r="AE972" s="101"/>
-      <c r="AF972" s="101"/>
-      <c r="AG972" s="101"/>
-      <c r="AH972" s="101"/>
-      <c r="AI972" s="101"/>
+      <c r="T972" s="103"/>
+      <c r="U972" s="103"/>
+      <c r="V972" s="103"/>
+      <c r="W972" s="103"/>
+      <c r="X972" s="103"/>
+      <c r="Y972" s="103"/>
+      <c r="Z972" s="103"/>
+      <c r="AA972" s="103"/>
+      <c r="AB972" s="103"/>
+      <c r="AC972" s="103"/>
+      <c r="AD972" s="103"/>
+      <c r="AE972" s="103"/>
+      <c r="AF972" s="103"/>
+      <c r="AG972" s="103"/>
+      <c r="AH972" s="103"/>
+      <c r="AI972" s="103"/>
     </row>
     <row r="973" ht="20.25" customHeight="1">
       <c r="A973" s="5"/>
       <c r="B973" s="5"/>
       <c r="C973" s="5"/>
       <c r="D973" s="5"/>
-      <c r="E973" s="99"/>
-      <c r="F973" s="99"/>
+      <c r="E973" s="101"/>
+      <c r="F973" s="101"/>
       <c r="G973" s="5"/>
       <c r="H973" s="5"/>
       <c r="I973" s="5"/>
       <c r="J973" s="5"/>
-      <c r="K973" s="100"/>
+      <c r="K973" s="102"/>
       <c r="L973" s="5"/>
       <c r="M973" s="5"/>
       <c r="N973" s="5"/>
@@ -77868,35 +78077,35 @@
       <c r="Q973" s="5"/>
       <c r="R973" s="5"/>
       <c r="S973" s="5"/>
-      <c r="T973" s="101"/>
-      <c r="U973" s="101"/>
-      <c r="V973" s="101"/>
-      <c r="W973" s="101"/>
-      <c r="X973" s="101"/>
-      <c r="Y973" s="101"/>
-      <c r="Z973" s="101"/>
-      <c r="AA973" s="101"/>
-      <c r="AB973" s="101"/>
-      <c r="AC973" s="101"/>
-      <c r="AD973" s="101"/>
-      <c r="AE973" s="101"/>
-      <c r="AF973" s="101"/>
-      <c r="AG973" s="101"/>
-      <c r="AH973" s="101"/>
-      <c r="AI973" s="101"/>
+      <c r="T973" s="103"/>
+      <c r="U973" s="103"/>
+      <c r="V973" s="103"/>
+      <c r="W973" s="103"/>
+      <c r="X973" s="103"/>
+      <c r="Y973" s="103"/>
+      <c r="Z973" s="103"/>
+      <c r="AA973" s="103"/>
+      <c r="AB973" s="103"/>
+      <c r="AC973" s="103"/>
+      <c r="AD973" s="103"/>
+      <c r="AE973" s="103"/>
+      <c r="AF973" s="103"/>
+      <c r="AG973" s="103"/>
+      <c r="AH973" s="103"/>
+      <c r="AI973" s="103"/>
     </row>
     <row r="974" ht="20.25" customHeight="1">
       <c r="A974" s="5"/>
       <c r="B974" s="5"/>
       <c r="C974" s="5"/>
       <c r="D974" s="5"/>
-      <c r="E974" s="99"/>
-      <c r="F974" s="99"/>
+      <c r="E974" s="101"/>
+      <c r="F974" s="101"/>
       <c r="G974" s="5"/>
       <c r="H974" s="5"/>
       <c r="I974" s="5"/>
       <c r="J974" s="5"/>
-      <c r="K974" s="100"/>
+      <c r="K974" s="102"/>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
       <c r="N974" s="5"/>
@@ -77905,35 +78114,35 @@
       <c r="Q974" s="5"/>
       <c r="R974" s="5"/>
       <c r="S974" s="5"/>
-      <c r="T974" s="101"/>
-      <c r="U974" s="101"/>
-      <c r="V974" s="101"/>
-      <c r="W974" s="101"/>
-      <c r="X974" s="101"/>
-      <c r="Y974" s="101"/>
-      <c r="Z974" s="101"/>
-      <c r="AA974" s="101"/>
-      <c r="AB974" s="101"/>
-      <c r="AC974" s="101"/>
-      <c r="AD974" s="101"/>
-      <c r="AE974" s="101"/>
-      <c r="AF974" s="101"/>
-      <c r="AG974" s="101"/>
-      <c r="AH974" s="101"/>
-      <c r="AI974" s="101"/>
+      <c r="T974" s="103"/>
+      <c r="U974" s="103"/>
+      <c r="V974" s="103"/>
+      <c r="W974" s="103"/>
+      <c r="X974" s="103"/>
+      <c r="Y974" s="103"/>
+      <c r="Z974" s="103"/>
+      <c r="AA974" s="103"/>
+      <c r="AB974" s="103"/>
+      <c r="AC974" s="103"/>
+      <c r="AD974" s="103"/>
+      <c r="AE974" s="103"/>
+      <c r="AF974" s="103"/>
+      <c r="AG974" s="103"/>
+      <c r="AH974" s="103"/>
+      <c r="AI974" s="103"/>
     </row>
     <row r="975" ht="20.25" customHeight="1">
       <c r="A975" s="5"/>
       <c r="B975" s="5"/>
       <c r="C975" s="5"/>
       <c r="D975" s="5"/>
-      <c r="E975" s="99"/>
-      <c r="F975" s="99"/>
+      <c r="E975" s="101"/>
+      <c r="F975" s="101"/>
       <c r="G975" s="5"/>
       <c r="H975" s="5"/>
       <c r="I975" s="5"/>
       <c r="J975" s="5"/>
-      <c r="K975" s="100"/>
+      <c r="K975" s="102"/>
       <c r="L975" s="5"/>
       <c r="M975" s="5"/>
       <c r="N975" s="5"/>
@@ -77942,35 +78151,35 @@
       <c r="Q975" s="5"/>
       <c r="R975" s="5"/>
       <c r="S975" s="5"/>
-      <c r="T975" s="101"/>
-      <c r="U975" s="101"/>
-      <c r="V975" s="101"/>
-      <c r="W975" s="101"/>
-      <c r="X975" s="101"/>
-      <c r="Y975" s="101"/>
-      <c r="Z975" s="101"/>
-      <c r="AA975" s="101"/>
-      <c r="AB975" s="101"/>
-      <c r="AC975" s="101"/>
-      <c r="AD975" s="101"/>
-      <c r="AE975" s="101"/>
-      <c r="AF975" s="101"/>
-      <c r="AG975" s="101"/>
-      <c r="AH975" s="101"/>
-      <c r="AI975" s="101"/>
+      <c r="T975" s="103"/>
+      <c r="U975" s="103"/>
+      <c r="V975" s="103"/>
+      <c r="W975" s="103"/>
+      <c r="X975" s="103"/>
+      <c r="Y975" s="103"/>
+      <c r="Z975" s="103"/>
+      <c r="AA975" s="103"/>
+      <c r="AB975" s="103"/>
+      <c r="AC975" s="103"/>
+      <c r="AD975" s="103"/>
+      <c r="AE975" s="103"/>
+      <c r="AF975" s="103"/>
+      <c r="AG975" s="103"/>
+      <c r="AH975" s="103"/>
+      <c r="AI975" s="103"/>
     </row>
     <row r="976" ht="20.25" customHeight="1">
       <c r="A976" s="5"/>
       <c r="B976" s="5"/>
       <c r="C976" s="5"/>
       <c r="D976" s="5"/>
-      <c r="E976" s="99"/>
-      <c r="F976" s="99"/>
+      <c r="E976" s="101"/>
+      <c r="F976" s="101"/>
       <c r="G976" s="5"/>
       <c r="H976" s="5"/>
       <c r="I976" s="5"/>
       <c r="J976" s="5"/>
-      <c r="K976" s="100"/>
+      <c r="K976" s="102"/>
       <c r="L976" s="5"/>
       <c r="M976" s="5"/>
       <c r="N976" s="5"/>
@@ -77979,35 +78188,35 @@
       <c r="Q976" s="5"/>
       <c r="R976" s="5"/>
       <c r="S976" s="5"/>
-      <c r="T976" s="101"/>
-      <c r="U976" s="101"/>
-      <c r="V976" s="101"/>
-      <c r="W976" s="101"/>
-      <c r="X976" s="101"/>
-      <c r="Y976" s="101"/>
-      <c r="Z976" s="101"/>
-      <c r="AA976" s="101"/>
-      <c r="AB976" s="101"/>
-      <c r="AC976" s="101"/>
-      <c r="AD976" s="101"/>
-      <c r="AE976" s="101"/>
-      <c r="AF976" s="101"/>
-      <c r="AG976" s="101"/>
-      <c r="AH976" s="101"/>
-      <c r="AI976" s="101"/>
+      <c r="T976" s="103"/>
+      <c r="U976" s="103"/>
+      <c r="V976" s="103"/>
+      <c r="W976" s="103"/>
+      <c r="X976" s="103"/>
+      <c r="Y976" s="103"/>
+      <c r="Z976" s="103"/>
+      <c r="AA976" s="103"/>
+      <c r="AB976" s="103"/>
+      <c r="AC976" s="103"/>
+      <c r="AD976" s="103"/>
+      <c r="AE976" s="103"/>
+      <c r="AF976" s="103"/>
+      <c r="AG976" s="103"/>
+      <c r="AH976" s="103"/>
+      <c r="AI976" s="103"/>
     </row>
     <row r="977" ht="20.25" customHeight="1">
       <c r="A977" s="5"/>
       <c r="B977" s="5"/>
       <c r="C977" s="5"/>
       <c r="D977" s="5"/>
-      <c r="E977" s="99"/>
-      <c r="F977" s="99"/>
+      <c r="E977" s="101"/>
+      <c r="F977" s="101"/>
       <c r="G977" s="5"/>
       <c r="H977" s="5"/>
       <c r="I977" s="5"/>
       <c r="J977" s="5"/>
-      <c r="K977" s="100"/>
+      <c r="K977" s="102"/>
       <c r="L977" s="5"/>
       <c r="M977" s="5"/>
       <c r="N977" s="5"/>
@@ -78016,35 +78225,35 @@
       <c r="Q977" s="5"/>
       <c r="R977" s="5"/>
       <c r="S977" s="5"/>
-      <c r="T977" s="101"/>
-      <c r="U977" s="101"/>
-      <c r="V977" s="101"/>
-      <c r="W977" s="101"/>
-      <c r="X977" s="101"/>
-      <c r="Y977" s="101"/>
-      <c r="Z977" s="101"/>
-      <c r="AA977" s="101"/>
-      <c r="AB977" s="101"/>
-      <c r="AC977" s="101"/>
-      <c r="AD977" s="101"/>
-      <c r="AE977" s="101"/>
-      <c r="AF977" s="101"/>
-      <c r="AG977" s="101"/>
-      <c r="AH977" s="101"/>
-      <c r="AI977" s="101"/>
+      <c r="T977" s="103"/>
+      <c r="U977" s="103"/>
+      <c r="V977" s="103"/>
+      <c r="W977" s="103"/>
+      <c r="X977" s="103"/>
+      <c r="Y977" s="103"/>
+      <c r="Z977" s="103"/>
+      <c r="AA977" s="103"/>
+      <c r="AB977" s="103"/>
+      <c r="AC977" s="103"/>
+      <c r="AD977" s="103"/>
+      <c r="AE977" s="103"/>
+      <c r="AF977" s="103"/>
+      <c r="AG977" s="103"/>
+      <c r="AH977" s="103"/>
+      <c r="AI977" s="103"/>
     </row>
     <row r="978" ht="20.25" customHeight="1">
       <c r="A978" s="5"/>
       <c r="B978" s="5"/>
       <c r="C978" s="5"/>
       <c r="D978" s="5"/>
-      <c r="E978" s="99"/>
-      <c r="F978" s="99"/>
+      <c r="E978" s="101"/>
+      <c r="F978" s="101"/>
       <c r="G978" s="5"/>
       <c r="H978" s="5"/>
       <c r="I978" s="5"/>
       <c r="J978" s="5"/>
-      <c r="K978" s="100"/>
+      <c r="K978" s="102"/>
       <c r="L978" s="5"/>
       <c r="M978" s="5"/>
       <c r="N978" s="5"/>
@@ -78053,35 +78262,35 @@
       <c r="Q978" s="5"/>
       <c r="R978" s="5"/>
       <c r="S978" s="5"/>
-      <c r="T978" s="101"/>
-      <c r="U978" s="101"/>
-      <c r="V978" s="101"/>
-      <c r="W978" s="101"/>
-      <c r="X978" s="101"/>
-      <c r="Y978" s="101"/>
-      <c r="Z978" s="101"/>
-      <c r="AA978" s="101"/>
-      <c r="AB978" s="101"/>
-      <c r="AC978" s="101"/>
-      <c r="AD978" s="101"/>
-      <c r="AE978" s="101"/>
-      <c r="AF978" s="101"/>
-      <c r="AG978" s="101"/>
-      <c r="AH978" s="101"/>
-      <c r="AI978" s="101"/>
+      <c r="T978" s="103"/>
+      <c r="U978" s="103"/>
+      <c r="V978" s="103"/>
+      <c r="W978" s="103"/>
+      <c r="X978" s="103"/>
+      <c r="Y978" s="103"/>
+      <c r="Z978" s="103"/>
+      <c r="AA978" s="103"/>
+      <c r="AB978" s="103"/>
+      <c r="AC978" s="103"/>
+      <c r="AD978" s="103"/>
+      <c r="AE978" s="103"/>
+      <c r="AF978" s="103"/>
+      <c r="AG978" s="103"/>
+      <c r="AH978" s="103"/>
+      <c r="AI978" s="103"/>
     </row>
     <row r="979" ht="20.25" customHeight="1">
       <c r="A979" s="5"/>
       <c r="B979" s="5"/>
       <c r="C979" s="5"/>
       <c r="D979" s="5"/>
-      <c r="E979" s="99"/>
-      <c r="F979" s="99"/>
+      <c r="E979" s="101"/>
+      <c r="F979" s="101"/>
       <c r="G979" s="5"/>
       <c r="H979" s="5"/>
       <c r="I979" s="5"/>
       <c r="J979" s="5"/>
-      <c r="K979" s="100"/>
+      <c r="K979" s="102"/>
       <c r="L979" s="5"/>
       <c r="M979" s="5"/>
       <c r="N979" s="5"/>
@@ -78090,35 +78299,35 @@
       <c r="Q979" s="5"/>
       <c r="R979" s="5"/>
       <c r="S979" s="5"/>
-      <c r="T979" s="101"/>
-      <c r="U979" s="101"/>
-      <c r="V979" s="101"/>
-      <c r="W979" s="101"/>
-      <c r="X979" s="101"/>
-      <c r="Y979" s="101"/>
-      <c r="Z979" s="101"/>
-      <c r="AA979" s="101"/>
-      <c r="AB979" s="101"/>
-      <c r="AC979" s="101"/>
-      <c r="AD979" s="101"/>
-      <c r="AE979" s="101"/>
-      <c r="AF979" s="101"/>
-      <c r="AG979" s="101"/>
-      <c r="AH979" s="101"/>
-      <c r="AI979" s="101"/>
+      <c r="T979" s="103"/>
+      <c r="U979" s="103"/>
+      <c r="V979" s="103"/>
+      <c r="W979" s="103"/>
+      <c r="X979" s="103"/>
+      <c r="Y979" s="103"/>
+      <c r="Z979" s="103"/>
+      <c r="AA979" s="103"/>
+      <c r="AB979" s="103"/>
+      <c r="AC979" s="103"/>
+      <c r="AD979" s="103"/>
+      <c r="AE979" s="103"/>
+      <c r="AF979" s="103"/>
+      <c r="AG979" s="103"/>
+      <c r="AH979" s="103"/>
+      <c r="AI979" s="103"/>
     </row>
     <row r="980" ht="20.25" customHeight="1">
       <c r="A980" s="5"/>
       <c r="B980" s="5"/>
       <c r="C980" s="5"/>
       <c r="D980" s="5"/>
-      <c r="E980" s="99"/>
-      <c r="F980" s="99"/>
+      <c r="E980" s="101"/>
+      <c r="F980" s="101"/>
       <c r="G980" s="5"/>
       <c r="H980" s="5"/>
       <c r="I980" s="5"/>
       <c r="J980" s="5"/>
-      <c r="K980" s="100"/>
+      <c r="K980" s="102"/>
       <c r="L980" s="5"/>
       <c r="M980" s="5"/>
       <c r="N980" s="5"/>
@@ -78127,35 +78336,35 @@
       <c r="Q980" s="5"/>
       <c r="R980" s="5"/>
       <c r="S980" s="5"/>
-      <c r="T980" s="101"/>
-      <c r="U980" s="101"/>
-      <c r="V980" s="101"/>
-      <c r="W980" s="101"/>
-      <c r="X980" s="101"/>
-      <c r="Y980" s="101"/>
-      <c r="Z980" s="101"/>
-      <c r="AA980" s="101"/>
-      <c r="AB980" s="101"/>
-      <c r="AC980" s="101"/>
-      <c r="AD980" s="101"/>
-      <c r="AE980" s="101"/>
-      <c r="AF980" s="101"/>
-      <c r="AG980" s="101"/>
-      <c r="AH980" s="101"/>
-      <c r="AI980" s="101"/>
+      <c r="T980" s="103"/>
+      <c r="U980" s="103"/>
+      <c r="V980" s="103"/>
+      <c r="W980" s="103"/>
+      <c r="X980" s="103"/>
+      <c r="Y980" s="103"/>
+      <c r="Z980" s="103"/>
+      <c r="AA980" s="103"/>
+      <c r="AB980" s="103"/>
+      <c r="AC980" s="103"/>
+      <c r="AD980" s="103"/>
+      <c r="AE980" s="103"/>
+      <c r="AF980" s="103"/>
+      <c r="AG980" s="103"/>
+      <c r="AH980" s="103"/>
+      <c r="AI980" s="103"/>
     </row>
     <row r="981" ht="20.25" customHeight="1">
       <c r="A981" s="5"/>
       <c r="B981" s="5"/>
       <c r="C981" s="5"/>
       <c r="D981" s="5"/>
-      <c r="E981" s="99"/>
-      <c r="F981" s="99"/>
+      <c r="E981" s="101"/>
+      <c r="F981" s="101"/>
       <c r="G981" s="5"/>
       <c r="H981" s="5"/>
       <c r="I981" s="5"/>
       <c r="J981" s="5"/>
-      <c r="K981" s="100"/>
+      <c r="K981" s="102"/>
       <c r="L981" s="5"/>
       <c r="M981" s="5"/>
       <c r="N981" s="5"/>
@@ -78164,35 +78373,35 @@
       <c r="Q981" s="5"/>
       <c r="R981" s="5"/>
       <c r="S981" s="5"/>
-      <c r="T981" s="101"/>
-      <c r="U981" s="101"/>
-      <c r="V981" s="101"/>
-      <c r="W981" s="101"/>
-      <c r="X981" s="101"/>
-      <c r="Y981" s="101"/>
-      <c r="Z981" s="101"/>
-      <c r="AA981" s="101"/>
-      <c r="AB981" s="101"/>
-      <c r="AC981" s="101"/>
-      <c r="AD981" s="101"/>
-      <c r="AE981" s="101"/>
-      <c r="AF981" s="101"/>
-      <c r="AG981" s="101"/>
-      <c r="AH981" s="101"/>
-      <c r="AI981" s="101"/>
+      <c r="T981" s="103"/>
+      <c r="U981" s="103"/>
+      <c r="V981" s="103"/>
+      <c r="W981" s="103"/>
+      <c r="X981" s="103"/>
+      <c r="Y981" s="103"/>
+      <c r="Z981" s="103"/>
+      <c r="AA981" s="103"/>
+      <c r="AB981" s="103"/>
+      <c r="AC981" s="103"/>
+      <c r="AD981" s="103"/>
+      <c r="AE981" s="103"/>
+      <c r="AF981" s="103"/>
+      <c r="AG981" s="103"/>
+      <c r="AH981" s="103"/>
+      <c r="AI981" s="103"/>
     </row>
     <row r="982" ht="20.25" customHeight="1">
       <c r="A982" s="5"/>
       <c r="B982" s="5"/>
       <c r="C982" s="5"/>
       <c r="D982" s="5"/>
-      <c r="E982" s="99"/>
-      <c r="F982" s="99"/>
+      <c r="E982" s="101"/>
+      <c r="F982" s="101"/>
       <c r="G982" s="5"/>
       <c r="H982" s="5"/>
       <c r="I982" s="5"/>
       <c r="J982" s="5"/>
-      <c r="K982" s="100"/>
+      <c r="K982" s="102"/>
       <c r="L982" s="5"/>
       <c r="M982" s="5"/>
       <c r="N982" s="5"/>
@@ -78201,35 +78410,35 @@
       <c r="Q982" s="5"/>
       <c r="R982" s="5"/>
       <c r="S982" s="5"/>
-      <c r="T982" s="101"/>
-      <c r="U982" s="101"/>
-      <c r="V982" s="101"/>
-      <c r="W982" s="101"/>
-      <c r="X982" s="101"/>
-      <c r="Y982" s="101"/>
-      <c r="Z982" s="101"/>
-      <c r="AA982" s="101"/>
-      <c r="AB982" s="101"/>
-      <c r="AC982" s="101"/>
-      <c r="AD982" s="101"/>
-      <c r="AE982" s="101"/>
-      <c r="AF982" s="101"/>
-      <c r="AG982" s="101"/>
-      <c r="AH982" s="101"/>
-      <c r="AI982" s="101"/>
+      <c r="T982" s="103"/>
+      <c r="U982" s="103"/>
+      <c r="V982" s="103"/>
+      <c r="W982" s="103"/>
+      <c r="X982" s="103"/>
+      <c r="Y982" s="103"/>
+      <c r="Z982" s="103"/>
+      <c r="AA982" s="103"/>
+      <c r="AB982" s="103"/>
+      <c r="AC982" s="103"/>
+      <c r="AD982" s="103"/>
+      <c r="AE982" s="103"/>
+      <c r="AF982" s="103"/>
+      <c r="AG982" s="103"/>
+      <c r="AH982" s="103"/>
+      <c r="AI982" s="103"/>
     </row>
     <row r="983" ht="20.25" customHeight="1">
       <c r="A983" s="5"/>
       <c r="B983" s="5"/>
       <c r="C983" s="5"/>
       <c r="D983" s="5"/>
-      <c r="E983" s="99"/>
-      <c r="F983" s="99"/>
+      <c r="E983" s="101"/>
+      <c r="F983" s="101"/>
       <c r="G983" s="5"/>
       <c r="H983" s="5"/>
       <c r="I983" s="5"/>
       <c r="J983" s="5"/>
-      <c r="K983" s="100"/>
+      <c r="K983" s="102"/>
       <c r="L983" s="5"/>
       <c r="M983" s="5"/>
       <c r="N983" s="5"/>
@@ -78238,35 +78447,35 @@
       <c r="Q983" s="5"/>
       <c r="R983" s="5"/>
       <c r="S983" s="5"/>
-      <c r="T983" s="101"/>
-      <c r="U983" s="101"/>
-      <c r="V983" s="101"/>
-      <c r="W983" s="101"/>
-      <c r="X983" s="101"/>
-      <c r="Y983" s="101"/>
-      <c r="Z983" s="101"/>
-      <c r="AA983" s="101"/>
-      <c r="AB983" s="101"/>
-      <c r="AC983" s="101"/>
-      <c r="AD983" s="101"/>
-      <c r="AE983" s="101"/>
-      <c r="AF983" s="101"/>
-      <c r="AG983" s="101"/>
-      <c r="AH983" s="101"/>
-      <c r="AI983" s="101"/>
+      <c r="T983" s="103"/>
+      <c r="U983" s="103"/>
+      <c r="V983" s="103"/>
+      <c r="W983" s="103"/>
+      <c r="X983" s="103"/>
+      <c r="Y983" s="103"/>
+      <c r="Z983" s="103"/>
+      <c r="AA983" s="103"/>
+      <c r="AB983" s="103"/>
+      <c r="AC983" s="103"/>
+      <c r="AD983" s="103"/>
+      <c r="AE983" s="103"/>
+      <c r="AF983" s="103"/>
+      <c r="AG983" s="103"/>
+      <c r="AH983" s="103"/>
+      <c r="AI983" s="103"/>
     </row>
     <row r="984" ht="20.25" customHeight="1">
       <c r="A984" s="5"/>
       <c r="B984" s="5"/>
       <c r="C984" s="5"/>
       <c r="D984" s="5"/>
-      <c r="E984" s="99"/>
-      <c r="F984" s="99"/>
+      <c r="E984" s="101"/>
+      <c r="F984" s="101"/>
       <c r="G984" s="5"/>
       <c r="H984" s="5"/>
       <c r="I984" s="5"/>
       <c r="J984" s="5"/>
-      <c r="K984" s="100"/>
+      <c r="K984" s="102"/>
       <c r="L984" s="5"/>
       <c r="M984" s="5"/>
       <c r="N984" s="5"/>
@@ -78275,35 +78484,35 @@
       <c r="Q984" s="5"/>
       <c r="R984" s="5"/>
       <c r="S984" s="5"/>
-      <c r="T984" s="101"/>
-      <c r="U984" s="101"/>
-      <c r="V984" s="101"/>
-      <c r="W984" s="101"/>
-      <c r="X984" s="101"/>
-      <c r="Y984" s="101"/>
-      <c r="Z984" s="101"/>
-      <c r="AA984" s="101"/>
-      <c r="AB984" s="101"/>
-      <c r="AC984" s="101"/>
-      <c r="AD984" s="101"/>
-      <c r="AE984" s="101"/>
-      <c r="AF984" s="101"/>
-      <c r="AG984" s="101"/>
-      <c r="AH984" s="101"/>
-      <c r="AI984" s="101"/>
+      <c r="T984" s="103"/>
+      <c r="U984" s="103"/>
+      <c r="V984" s="103"/>
+      <c r="W984" s="103"/>
+      <c r="X984" s="103"/>
+      <c r="Y984" s="103"/>
+      <c r="Z984" s="103"/>
+      <c r="AA984" s="103"/>
+      <c r="AB984" s="103"/>
+      <c r="AC984" s="103"/>
+      <c r="AD984" s="103"/>
+      <c r="AE984" s="103"/>
+      <c r="AF984" s="103"/>
+      <c r="AG984" s="103"/>
+      <c r="AH984" s="103"/>
+      <c r="AI984" s="103"/>
     </row>
     <row r="985" ht="20.25" customHeight="1">
       <c r="A985" s="5"/>
       <c r="B985" s="5"/>
       <c r="C985" s="5"/>
       <c r="D985" s="5"/>
-      <c r="E985" s="99"/>
-      <c r="F985" s="99"/>
+      <c r="E985" s="101"/>
+      <c r="F985" s="101"/>
       <c r="G985" s="5"/>
       <c r="H985" s="5"/>
       <c r="I985" s="5"/>
       <c r="J985" s="5"/>
-      <c r="K985" s="100"/>
+      <c r="K985" s="102"/>
       <c r="L985" s="5"/>
       <c r="M985" s="5"/>
       <c r="N985" s="5"/>
@@ -78312,35 +78521,35 @@
       <c r="Q985" s="5"/>
       <c r="R985" s="5"/>
       <c r="S985" s="5"/>
-      <c r="T985" s="101"/>
-      <c r="U985" s="101"/>
-      <c r="V985" s="101"/>
-      <c r="W985" s="101"/>
-      <c r="X985" s="101"/>
-      <c r="Y985" s="101"/>
-      <c r="Z985" s="101"/>
-      <c r="AA985" s="101"/>
-      <c r="AB985" s="101"/>
-      <c r="AC985" s="101"/>
-      <c r="AD985" s="101"/>
-      <c r="AE985" s="101"/>
-      <c r="AF985" s="101"/>
-      <c r="AG985" s="101"/>
-      <c r="AH985" s="101"/>
-      <c r="AI985" s="101"/>
+      <c r="T985" s="103"/>
+      <c r="U985" s="103"/>
+      <c r="V985" s="103"/>
+      <c r="W985" s="103"/>
+      <c r="X985" s="103"/>
+      <c r="Y985" s="103"/>
+      <c r="Z985" s="103"/>
+      <c r="AA985" s="103"/>
+      <c r="AB985" s="103"/>
+      <c r="AC985" s="103"/>
+      <c r="AD985" s="103"/>
+      <c r="AE985" s="103"/>
+      <c r="AF985" s="103"/>
+      <c r="AG985" s="103"/>
+      <c r="AH985" s="103"/>
+      <c r="AI985" s="103"/>
     </row>
     <row r="986" ht="20.25" customHeight="1">
       <c r="A986" s="5"/>
       <c r="B986" s="5"/>
       <c r="C986" s="5"/>
       <c r="D986" s="5"/>
-      <c r="E986" s="99"/>
-      <c r="F986" s="99"/>
+      <c r="E986" s="101"/>
+      <c r="F986" s="101"/>
       <c r="G986" s="5"/>
       <c r="H986" s="5"/>
       <c r="I986" s="5"/>
       <c r="J986" s="5"/>
-      <c r="K986" s="100"/>
+      <c r="K986" s="102"/>
       <c r="L986" s="5"/>
       <c r="M986" s="5"/>
       <c r="N986" s="5"/>
@@ -78349,35 +78558,35 @@
       <c r="Q986" s="5"/>
       <c r="R986" s="5"/>
       <c r="S986" s="5"/>
-      <c r="T986" s="101"/>
-      <c r="U986" s="101"/>
-      <c r="V986" s="101"/>
-      <c r="W986" s="101"/>
-      <c r="X986" s="101"/>
-      <c r="Y986" s="101"/>
-      <c r="Z986" s="101"/>
-      <c r="AA986" s="101"/>
-      <c r="AB986" s="101"/>
-      <c r="AC986" s="101"/>
-      <c r="AD986" s="101"/>
-      <c r="AE986" s="101"/>
-      <c r="AF986" s="101"/>
-      <c r="AG986" s="101"/>
-      <c r="AH986" s="101"/>
-      <c r="AI986" s="101"/>
+      <c r="T986" s="103"/>
+      <c r="U986" s="103"/>
+      <c r="V986" s="103"/>
+      <c r="W986" s="103"/>
+      <c r="X986" s="103"/>
+      <c r="Y986" s="103"/>
+      <c r="Z986" s="103"/>
+      <c r="AA986" s="103"/>
+      <c r="AB986" s="103"/>
+      <c r="AC986" s="103"/>
+      <c r="AD986" s="103"/>
+      <c r="AE986" s="103"/>
+      <c r="AF986" s="103"/>
+      <c r="AG986" s="103"/>
+      <c r="AH986" s="103"/>
+      <c r="AI986" s="103"/>
     </row>
     <row r="987" ht="20.25" customHeight="1">
       <c r="A987" s="5"/>
       <c r="B987" s="5"/>
       <c r="C987" s="5"/>
       <c r="D987" s="5"/>
-      <c r="E987" s="99"/>
-      <c r="F987" s="99"/>
+      <c r="E987" s="101"/>
+      <c r="F987" s="101"/>
       <c r="G987" s="5"/>
       <c r="H987" s="5"/>
       <c r="I987" s="5"/>
       <c r="J987" s="5"/>
-      <c r="K987" s="100"/>
+      <c r="K987" s="102"/>
       <c r="L987" s="5"/>
       <c r="M987" s="5"/>
       <c r="N987" s="5"/>
@@ -78386,35 +78595,35 @@
       <c r="Q987" s="5"/>
       <c r="R987" s="5"/>
       <c r="S987" s="5"/>
-      <c r="T987" s="101"/>
-      <c r="U987" s="101"/>
-      <c r="V987" s="101"/>
-      <c r="W987" s="101"/>
-      <c r="X987" s="101"/>
-      <c r="Y987" s="101"/>
-      <c r="Z987" s="101"/>
-      <c r="AA987" s="101"/>
-      <c r="AB987" s="101"/>
-      <c r="AC987" s="101"/>
-      <c r="AD987" s="101"/>
-      <c r="AE987" s="101"/>
-      <c r="AF987" s="101"/>
-      <c r="AG987" s="101"/>
-      <c r="AH987" s="101"/>
-      <c r="AI987" s="101"/>
+      <c r="T987" s="103"/>
+      <c r="U987" s="103"/>
+      <c r="V987" s="103"/>
+      <c r="W987" s="103"/>
+      <c r="X987" s="103"/>
+      <c r="Y987" s="103"/>
+      <c r="Z987" s="103"/>
+      <c r="AA987" s="103"/>
+      <c r="AB987" s="103"/>
+      <c r="AC987" s="103"/>
+      <c r="AD987" s="103"/>
+      <c r="AE987" s="103"/>
+      <c r="AF987" s="103"/>
+      <c r="AG987" s="103"/>
+      <c r="AH987" s="103"/>
+      <c r="AI987" s="103"/>
     </row>
     <row r="988" ht="20.25" customHeight="1">
       <c r="A988" s="5"/>
       <c r="B988" s="5"/>
       <c r="C988" s="5"/>
       <c r="D988" s="5"/>
-      <c r="E988" s="99"/>
-      <c r="F988" s="99"/>
+      <c r="E988" s="101"/>
+      <c r="F988" s="101"/>
       <c r="G988" s="5"/>
       <c r="H988" s="5"/>
       <c r="I988" s="5"/>
       <c r="J988" s="5"/>
-      <c r="K988" s="100"/>
+      <c r="K988" s="102"/>
       <c r="L988" s="5"/>
       <c r="M988" s="5"/>
       <c r="N988" s="5"/>
@@ -78423,35 +78632,35 @@
       <c r="Q988" s="5"/>
       <c r="R988" s="5"/>
       <c r="S988" s="5"/>
-      <c r="T988" s="101"/>
-      <c r="U988" s="101"/>
-      <c r="V988" s="101"/>
-      <c r="W988" s="101"/>
-      <c r="X988" s="101"/>
-      <c r="Y988" s="101"/>
-      <c r="Z988" s="101"/>
-      <c r="AA988" s="101"/>
-      <c r="AB988" s="101"/>
-      <c r="AC988" s="101"/>
-      <c r="AD988" s="101"/>
-      <c r="AE988" s="101"/>
-      <c r="AF988" s="101"/>
-      <c r="AG988" s="101"/>
-      <c r="AH988" s="101"/>
-      <c r="AI988" s="101"/>
+      <c r="T988" s="103"/>
+      <c r="U988" s="103"/>
+      <c r="V988" s="103"/>
+      <c r="W988" s="103"/>
+      <c r="X988" s="103"/>
+      <c r="Y988" s="103"/>
+      <c r="Z988" s="103"/>
+      <c r="AA988" s="103"/>
+      <c r="AB988" s="103"/>
+      <c r="AC988" s="103"/>
+      <c r="AD988" s="103"/>
+      <c r="AE988" s="103"/>
+      <c r="AF988" s="103"/>
+      <c r="AG988" s="103"/>
+      <c r="AH988" s="103"/>
+      <c r="AI988" s="103"/>
     </row>
     <row r="989" ht="20.25" customHeight="1">
       <c r="A989" s="5"/>
       <c r="B989" s="5"/>
       <c r="C989" s="5"/>
       <c r="D989" s="5"/>
-      <c r="E989" s="99"/>
-      <c r="F989" s="99"/>
+      <c r="E989" s="101"/>
+      <c r="F989" s="101"/>
       <c r="G989" s="5"/>
       <c r="H989" s="5"/>
       <c r="I989" s="5"/>
       <c r="J989" s="5"/>
-      <c r="K989" s="100"/>
+      <c r="K989" s="102"/>
       <c r="L989" s="5"/>
       <c r="M989" s="5"/>
       <c r="N989" s="5"/>
@@ -78460,35 +78669,35 @@
       <c r="Q989" s="5"/>
       <c r="R989" s="5"/>
       <c r="S989" s="5"/>
-      <c r="T989" s="101"/>
-      <c r="U989" s="101"/>
-      <c r="V989" s="101"/>
-      <c r="W989" s="101"/>
-      <c r="X989" s="101"/>
-      <c r="Y989" s="101"/>
-      <c r="Z989" s="101"/>
-      <c r="AA989" s="101"/>
-      <c r="AB989" s="101"/>
-      <c r="AC989" s="101"/>
-      <c r="AD989" s="101"/>
-      <c r="AE989" s="101"/>
-      <c r="AF989" s="101"/>
-      <c r="AG989" s="101"/>
-      <c r="AH989" s="101"/>
-      <c r="AI989" s="101"/>
+      <c r="T989" s="103"/>
+      <c r="U989" s="103"/>
+      <c r="V989" s="103"/>
+      <c r="W989" s="103"/>
+      <c r="X989" s="103"/>
+      <c r="Y989" s="103"/>
+      <c r="Z989" s="103"/>
+      <c r="AA989" s="103"/>
+      <c r="AB989" s="103"/>
+      <c r="AC989" s="103"/>
+      <c r="AD989" s="103"/>
+      <c r="AE989" s="103"/>
+      <c r="AF989" s="103"/>
+      <c r="AG989" s="103"/>
+      <c r="AH989" s="103"/>
+      <c r="AI989" s="103"/>
     </row>
     <row r="990" ht="20.25" customHeight="1">
       <c r="A990" s="5"/>
       <c r="B990" s="5"/>
       <c r="C990" s="5"/>
       <c r="D990" s="5"/>
-      <c r="E990" s="99"/>
-      <c r="F990" s="99"/>
+      <c r="E990" s="101"/>
+      <c r="F990" s="101"/>
       <c r="G990" s="5"/>
       <c r="H990" s="5"/>
       <c r="I990" s="5"/>
       <c r="J990" s="5"/>
-      <c r="K990" s="100"/>
+      <c r="K990" s="102"/>
       <c r="L990" s="5"/>
       <c r="M990" s="5"/>
       <c r="N990" s="5"/>
@@ -78497,35 +78706,35 @@
       <c r="Q990" s="5"/>
       <c r="R990" s="5"/>
       <c r="S990" s="5"/>
-      <c r="T990" s="101"/>
-      <c r="U990" s="101"/>
-      <c r="V990" s="101"/>
-      <c r="W990" s="101"/>
-      <c r="X990" s="101"/>
-      <c r="Y990" s="101"/>
-      <c r="Z990" s="101"/>
-      <c r="AA990" s="101"/>
-      <c r="AB990" s="101"/>
-      <c r="AC990" s="101"/>
-      <c r="AD990" s="101"/>
-      <c r="AE990" s="101"/>
-      <c r="AF990" s="101"/>
-      <c r="AG990" s="101"/>
-      <c r="AH990" s="101"/>
-      <c r="AI990" s="101"/>
+      <c r="T990" s="103"/>
+      <c r="U990" s="103"/>
+      <c r="V990" s="103"/>
+      <c r="W990" s="103"/>
+      <c r="X990" s="103"/>
+      <c r="Y990" s="103"/>
+      <c r="Z990" s="103"/>
+      <c r="AA990" s="103"/>
+      <c r="AB990" s="103"/>
+      <c r="AC990" s="103"/>
+      <c r="AD990" s="103"/>
+      <c r="AE990" s="103"/>
+      <c r="AF990" s="103"/>
+      <c r="AG990" s="103"/>
+      <c r="AH990" s="103"/>
+      <c r="AI990" s="103"/>
     </row>
     <row r="991" ht="20.25" customHeight="1">
       <c r="A991" s="5"/>
       <c r="B991" s="5"/>
       <c r="C991" s="5"/>
       <c r="D991" s="5"/>
-      <c r="E991" s="99"/>
-      <c r="F991" s="99"/>
+      <c r="E991" s="101"/>
+      <c r="F991" s="101"/>
       <c r="G991" s="5"/>
       <c r="H991" s="5"/>
       <c r="I991" s="5"/>
       <c r="J991" s="5"/>
-      <c r="K991" s="100"/>
+      <c r="K991" s="102"/>
       <c r="L991" s="5"/>
       <c r="M991" s="5"/>
       <c r="N991" s="5"/>
@@ -78534,35 +78743,35 @@
       <c r="Q991" s="5"/>
       <c r="R991" s="5"/>
       <c r="S991" s="5"/>
-      <c r="T991" s="101"/>
-      <c r="U991" s="101"/>
-      <c r="V991" s="101"/>
-      <c r="W991" s="101"/>
-      <c r="X991" s="101"/>
-      <c r="Y991" s="101"/>
-      <c r="Z991" s="101"/>
-      <c r="AA991" s="101"/>
-      <c r="AB991" s="101"/>
-      <c r="AC991" s="101"/>
-      <c r="AD991" s="101"/>
-      <c r="AE991" s="101"/>
-      <c r="AF991" s="101"/>
-      <c r="AG991" s="101"/>
-      <c r="AH991" s="101"/>
-      <c r="AI991" s="101"/>
+      <c r="T991" s="103"/>
+      <c r="U991" s="103"/>
+      <c r="V991" s="103"/>
+      <c r="W991" s="103"/>
+      <c r="X991" s="103"/>
+      <c r="Y991" s="103"/>
+      <c r="Z991" s="103"/>
+      <c r="AA991" s="103"/>
+      <c r="AB991" s="103"/>
+      <c r="AC991" s="103"/>
+      <c r="AD991" s="103"/>
+      <c r="AE991" s="103"/>
+      <c r="AF991" s="103"/>
+      <c r="AG991" s="103"/>
+      <c r="AH991" s="103"/>
+      <c r="AI991" s="103"/>
     </row>
     <row r="992" ht="20.25" customHeight="1">
       <c r="A992" s="5"/>
       <c r="B992" s="5"/>
       <c r="C992" s="5"/>
       <c r="D992" s="5"/>
-      <c r="E992" s="99"/>
-      <c r="F992" s="99"/>
+      <c r="E992" s="101"/>
+      <c r="F992" s="101"/>
       <c r="G992" s="5"/>
       <c r="H992" s="5"/>
       <c r="I992" s="5"/>
       <c r="J992" s="5"/>
-      <c r="K992" s="100"/>
+      <c r="K992" s="102"/>
       <c r="L992" s="5"/>
       <c r="M992" s="5"/>
       <c r="N992" s="5"/>
@@ -78571,35 +78780,35 @@
       <c r="Q992" s="5"/>
       <c r="R992" s="5"/>
       <c r="S992" s="5"/>
-      <c r="T992" s="101"/>
-      <c r="U992" s="101"/>
-      <c r="V992" s="101"/>
-      <c r="W992" s="101"/>
-      <c r="X992" s="101"/>
-      <c r="Y992" s="101"/>
-      <c r="Z992" s="101"/>
-      <c r="AA992" s="101"/>
-      <c r="AB992" s="101"/>
-      <c r="AC992" s="101"/>
-      <c r="AD992" s="101"/>
-      <c r="AE992" s="101"/>
-      <c r="AF992" s="101"/>
-      <c r="AG992" s="101"/>
-      <c r="AH992" s="101"/>
-      <c r="AI992" s="101"/>
+      <c r="T992" s="103"/>
+      <c r="U992" s="103"/>
+      <c r="V992" s="103"/>
+      <c r="W992" s="103"/>
+      <c r="X992" s="103"/>
+      <c r="Y992" s="103"/>
+      <c r="Z992" s="103"/>
+      <c r="AA992" s="103"/>
+      <c r="AB992" s="103"/>
+      <c r="AC992" s="103"/>
+      <c r="AD992" s="103"/>
+      <c r="AE992" s="103"/>
+      <c r="AF992" s="103"/>
+      <c r="AG992" s="103"/>
+      <c r="AH992" s="103"/>
+      <c r="AI992" s="103"/>
     </row>
     <row r="993" ht="20.25" customHeight="1">
       <c r="A993" s="5"/>
       <c r="B993" s="5"/>
       <c r="C993" s="5"/>
       <c r="D993" s="5"/>
-      <c r="E993" s="99"/>
-      <c r="F993" s="99"/>
+      <c r="E993" s="101"/>
+      <c r="F993" s="101"/>
       <c r="G993" s="5"/>
       <c r="H993" s="5"/>
       <c r="I993" s="5"/>
       <c r="J993" s="5"/>
-      <c r="K993" s="100"/>
+      <c r="K993" s="102"/>
       <c r="L993" s="5"/>
       <c r="M993" s="5"/>
       <c r="N993" s="5"/>
@@ -78608,35 +78817,35 @@
       <c r="Q993" s="5"/>
       <c r="R993" s="5"/>
       <c r="S993" s="5"/>
-      <c r="T993" s="101"/>
-      <c r="U993" s="101"/>
-      <c r="V993" s="101"/>
-      <c r="W993" s="101"/>
-      <c r="X993" s="101"/>
-      <c r="Y993" s="101"/>
-      <c r="Z993" s="101"/>
-      <c r="AA993" s="101"/>
-      <c r="AB993" s="101"/>
-      <c r="AC993" s="101"/>
-      <c r="AD993" s="101"/>
-      <c r="AE993" s="101"/>
-      <c r="AF993" s="101"/>
-      <c r="AG993" s="101"/>
-      <c r="AH993" s="101"/>
-      <c r="AI993" s="101"/>
+      <c r="T993" s="103"/>
+      <c r="U993" s="103"/>
+      <c r="V993" s="103"/>
+      <c r="W993" s="103"/>
+      <c r="X993" s="103"/>
+      <c r="Y993" s="103"/>
+      <c r="Z993" s="103"/>
+      <c r="AA993" s="103"/>
+      <c r="AB993" s="103"/>
+      <c r="AC993" s="103"/>
+      <c r="AD993" s="103"/>
+      <c r="AE993" s="103"/>
+      <c r="AF993" s="103"/>
+      <c r="AG993" s="103"/>
+      <c r="AH993" s="103"/>
+      <c r="AI993" s="103"/>
     </row>
     <row r="994" ht="20.25" customHeight="1">
       <c r="A994" s="5"/>
       <c r="B994" s="5"/>
       <c r="C994" s="5"/>
       <c r="D994" s="5"/>
-      <c r="E994" s="99"/>
-      <c r="F994" s="99"/>
+      <c r="E994" s="101"/>
+      <c r="F994" s="101"/>
       <c r="G994" s="5"/>
       <c r="H994" s="5"/>
       <c r="I994" s="5"/>
       <c r="J994" s="5"/>
-      <c r="K994" s="100"/>
+      <c r="K994" s="102"/>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
       <c r="N994" s="5"/>
@@ -78645,68 +78854,31 @@
       <c r="Q994" s="5"/>
       <c r="R994" s="5"/>
       <c r="S994" s="5"/>
-      <c r="T994" s="101"/>
-      <c r="U994" s="101"/>
-      <c r="V994" s="101"/>
-      <c r="W994" s="101"/>
-      <c r="X994" s="101"/>
-      <c r="Y994" s="101"/>
-      <c r="Z994" s="101"/>
-      <c r="AA994" s="101"/>
-      <c r="AB994" s="101"/>
-      <c r="AC994" s="101"/>
-      <c r="AD994" s="101"/>
-      <c r="AE994" s="101"/>
-      <c r="AF994" s="101"/>
-      <c r="AG994" s="101"/>
-      <c r="AH994" s="101"/>
-      <c r="AI994" s="101"/>
-    </row>
-    <row r="995" ht="20.25" customHeight="1">
-      <c r="A995" s="5"/>
-      <c r="B995" s="5"/>
-      <c r="C995" s="5"/>
-      <c r="D995" s="5"/>
-      <c r="E995" s="99"/>
-      <c r="F995" s="99"/>
-      <c r="G995" s="5"/>
-      <c r="H995" s="5"/>
-      <c r="I995" s="5"/>
-      <c r="J995" s="5"/>
-      <c r="K995" s="100"/>
-      <c r="L995" s="5"/>
-      <c r="M995" s="5"/>
-      <c r="N995" s="5"/>
-      <c r="O995" s="5"/>
-      <c r="P995" s="5"/>
-      <c r="Q995" s="5"/>
-      <c r="R995" s="5"/>
-      <c r="S995" s="5"/>
-      <c r="T995" s="101"/>
-      <c r="U995" s="101"/>
-      <c r="V995" s="101"/>
-      <c r="W995" s="101"/>
-      <c r="X995" s="101"/>
-      <c r="Y995" s="101"/>
-      <c r="Z995" s="101"/>
-      <c r="AA995" s="101"/>
-      <c r="AB995" s="101"/>
-      <c r="AC995" s="101"/>
-      <c r="AD995" s="101"/>
-      <c r="AE995" s="101"/>
-      <c r="AF995" s="101"/>
-      <c r="AG995" s="101"/>
-      <c r="AH995" s="101"/>
-      <c r="AI995" s="101"/>
+      <c r="T994" s="103"/>
+      <c r="U994" s="103"/>
+      <c r="V994" s="103"/>
+      <c r="W994" s="103"/>
+      <c r="X994" s="103"/>
+      <c r="Y994" s="103"/>
+      <c r="Z994" s="103"/>
+      <c r="AA994" s="103"/>
+      <c r="AB994" s="103"/>
+      <c r="AC994" s="103"/>
+      <c r="AD994" s="103"/>
+      <c r="AE994" s="103"/>
+      <c r="AF994" s="103"/>
+      <c r="AG994" s="103"/>
+      <c r="AH994" s="103"/>
+      <c r="AI994" s="103"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$AI$932">
-    <sortState ref="A1:AI932">
-      <sortCondition ref="D1:D932"/>
-      <sortCondition ref="C1:C932"/>
+  <autoFilter ref="$A$1:$AI$935">
+    <sortState ref="A1:AI935">
+      <sortCondition ref="D1:D935"/>
+      <sortCondition ref="C1:C935"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="K1:K748 K750:K995">
+  <conditionalFormatting sqref="K1:K748 K750:K994">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>COUNTIF(K:K, K1)&gt;1</formula>
     </cfRule>
@@ -80764,7 +80936,24 @@
     <hyperlink r:id="rId2050" ref="V932"/>
     <hyperlink r:id="rId2051" ref="W932"/>
     <hyperlink r:id="rId2052" ref="X932"/>
+    <hyperlink r:id="rId2053" ref="S933"/>
+    <hyperlink r:id="rId2054" ref="T933"/>
+    <hyperlink r:id="rId2055" ref="AE933"/>
+    <hyperlink r:id="rId2056" ref="AF933"/>
+    <hyperlink r:id="rId2057" ref="S934"/>
+    <hyperlink r:id="rId2058" ref="T934"/>
+    <hyperlink r:id="rId2059" ref="U934"/>
+    <hyperlink r:id="rId2060" ref="AE934"/>
+    <hyperlink r:id="rId2061" ref="AF934"/>
+    <hyperlink r:id="rId2062" ref="AG934"/>
+    <hyperlink r:id="rId2063" ref="S935"/>
+    <hyperlink r:id="rId2064" ref="T935"/>
+    <hyperlink r:id="rId2065" ref="U935"/>
+    <hyperlink r:id="rId2066" ref="AE935"/>
+    <hyperlink r:id="rId2067" ref="AF935"/>
+    <hyperlink r:id="rId2068" ref="AG935"/>
+    <hyperlink r:id="rId2069" ref="AH935"/>
   </hyperlinks>
-  <drawing r:id="rId2053"/>
+  <drawing r:id="rId2070"/>
 </worksheet>
 </file>